--- a/research/traditional_assets/database/data/turkey/turkey_electronics_consumer_office.xlsx
+++ b/research/traditional_assets/database/data/turkey/turkey_electronics_consumer_office.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1597423457308191</v>
+        <v>0.1593767398664921</v>
       </c>
       <c r="C2">
-        <v>2303.262399469404</v>
+        <v>2287.280848502468</v>
       </c>
       <c r="D2">
-        <v>2164.462399469404</v>
+        <v>2171.429848502468</v>
       </c>
       <c r="E2">
-        <v>-1618.7</v>
+        <v>-1595.751</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>22.949</v>
       </c>
       <c r="G2">
         <v>138.8</v>
@@ -1439,28 +1439,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.1543347</v>
       </c>
       <c r="N2">
-        <v>375.4333333333333</v>
+        <v>374.2789986333333</v>
       </c>
       <c r="O2">
-        <v>93.85833333333333</v>
+        <v>93.56974965833334</v>
       </c>
       <c r="P2">
-        <v>281.575</v>
+        <v>280.709248975</v>
       </c>
       <c r="Q2">
-        <v>363.475</v>
+        <v>362.609248975</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1597423457308191</v>
+        <v>0.160605545319689</v>
       </c>
       <c r="T2">
-        <v>1.101909567345926</v>
+        <v>1.110257367098547</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>325.2378476825945</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1593767398664921</v>
+        <v>0.159011134002165</v>
       </c>
       <c r="C3">
-        <v>2287.280848502468</v>
+        <v>2271.344299120374</v>
       </c>
       <c r="D3">
-        <v>2171.429848502468</v>
+        <v>2178.442299120374</v>
       </c>
       <c r="E3">
-        <v>-1595.751</v>
+        <v>-1572.802</v>
       </c>
       <c r="F3">
-        <v>22.949</v>
+        <v>45.898</v>
       </c>
       <c r="G3">
         <v>138.8</v>
@@ -1521,28 +1521,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M3">
-        <v>1.1543347</v>
+        <v>2.3086694</v>
       </c>
       <c r="N3">
-        <v>374.2789986333333</v>
+        <v>373.1246639333334</v>
       </c>
       <c r="O3">
-        <v>93.56974965833334</v>
+        <v>93.28116598333334</v>
       </c>
       <c r="P3">
-        <v>280.709248975</v>
+        <v>279.84349795</v>
       </c>
       <c r="Q3">
-        <v>362.609248975</v>
+        <v>361.74349795</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.160605545319689</v>
+        <v>0.161486361226699</v>
       </c>
       <c r="T3">
-        <v>1.110257367098547</v>
+        <v>1.118775530111425</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>325.2378476825945</v>
+        <v>162.6189238412972</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.159011134002165</v>
+        <v>0.1586455281378379</v>
       </c>
       <c r="C4">
-        <v>2271.344299120374</v>
+        <v>2255.4531887222</v>
       </c>
       <c r="D4">
-        <v>2178.442299120374</v>
+        <v>2185.5001887222</v>
       </c>
       <c r="E4">
-        <v>-1572.802</v>
+        <v>-1549.853</v>
       </c>
       <c r="F4">
-        <v>45.898</v>
+        <v>68.84699999999999</v>
       </c>
       <c r="G4">
         <v>138.8</v>
@@ -1603,28 +1603,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M4">
-        <v>2.3086694</v>
+        <v>3.4630041</v>
       </c>
       <c r="N4">
-        <v>373.1246639333334</v>
+        <v>371.9703292333334</v>
       </c>
       <c r="O4">
-        <v>93.28116598333334</v>
+        <v>92.99258230833334</v>
       </c>
       <c r="P4">
-        <v>279.84349795</v>
+        <v>278.977746925</v>
       </c>
       <c r="Q4">
-        <v>361.74349795</v>
+        <v>360.877746925</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.161486361226699</v>
+        <v>0.1623853382864309</v>
       </c>
       <c r="T4">
-        <v>1.118775530111425</v>
+        <v>1.127469325351373</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>162.6189238412972</v>
+        <v>108.4126158941982</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1586455281378379</v>
+        <v>0.158279922273511</v>
       </c>
       <c r="C5">
-        <v>2255.4531887222</v>
+        <v>2239.607960393927</v>
       </c>
       <c r="D5">
-        <v>2185.5001887222</v>
+        <v>2192.603960393927</v>
       </c>
       <c r="E5">
-        <v>-1549.853</v>
+        <v>-1526.904</v>
       </c>
       <c r="F5">
-        <v>68.84699999999999</v>
+        <v>91.79600000000001</v>
       </c>
       <c r="G5">
         <v>138.8</v>
@@ -1685,28 +1685,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M5">
-        <v>3.4630041</v>
+        <v>4.6173388</v>
       </c>
       <c r="N5">
-        <v>371.9703292333334</v>
+        <v>370.8159945333333</v>
       </c>
       <c r="O5">
-        <v>92.99258230833334</v>
+        <v>92.70399863333333</v>
       </c>
       <c r="P5">
-        <v>278.977746925</v>
+        <v>278.1119959</v>
       </c>
       <c r="Q5">
-        <v>360.877746925</v>
+        <v>360.0119959</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1623853382864309</v>
+        <v>0.1633030440349072</v>
       </c>
       <c r="T5">
-        <v>1.127469325351373</v>
+        <v>1.136344241325486</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>108.4126158941982</v>
+        <v>81.3094619206486</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.158279922273511</v>
+        <v>0.1579143164091839</v>
       </c>
       <c r="C6">
-        <v>2239.607960393927</v>
+        <v>2223.809063001172</v>
       </c>
       <c r="D6">
-        <v>2192.603960393927</v>
+        <v>2199.754063001172</v>
       </c>
       <c r="E6">
-        <v>-1526.904</v>
+        <v>-1503.955</v>
       </c>
       <c r="F6">
-        <v>91.79600000000001</v>
+        <v>114.745</v>
       </c>
       <c r="G6">
         <v>138.8</v>
@@ -1767,28 +1767,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M6">
-        <v>4.6173388</v>
+        <v>5.7716735</v>
       </c>
       <c r="N6">
-        <v>370.8159945333333</v>
+        <v>369.6616598333333</v>
       </c>
       <c r="O6">
-        <v>92.70399863333333</v>
+        <v>92.41541495833333</v>
       </c>
       <c r="P6">
-        <v>278.1119959</v>
+        <v>277.246244875</v>
       </c>
       <c r="Q6">
-        <v>360.0119959</v>
+        <v>359.146244875</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1633030440349072</v>
+        <v>0.1642400699044041</v>
       </c>
       <c r="T6">
-        <v>1.136344241325486</v>
+        <v>1.145405997635897</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>81.3094619206486</v>
+        <v>65.04756953651888</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1579143164091839</v>
+        <v>0.1575487105448568</v>
       </c>
       <c r="C7">
-        <v>2223.809063001172</v>
+        <v>2208.056951283723</v>
       </c>
       <c r="D7">
-        <v>2199.754063001172</v>
+        <v>2206.950951283723</v>
       </c>
       <c r="E7">
-        <v>-1503.955</v>
+        <v>-1481.006</v>
       </c>
       <c r="F7">
-        <v>114.745</v>
+        <v>137.694</v>
       </c>
       <c r="G7">
         <v>138.8</v>
@@ -1849,28 +1849,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M7">
-        <v>5.7716735</v>
+        <v>6.9260082</v>
       </c>
       <c r="N7">
-        <v>369.6616598333333</v>
+        <v>368.5073251333333</v>
       </c>
       <c r="O7">
-        <v>92.41541495833333</v>
+        <v>92.12683128333333</v>
       </c>
       <c r="P7">
-        <v>277.246244875</v>
+        <v>276.38049385</v>
       </c>
       <c r="Q7">
-        <v>359.146244875</v>
+        <v>358.28049385</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1642400699044041</v>
+        <v>0.1651970324945285</v>
       </c>
       <c r="T7">
-        <v>1.145405997635897</v>
+        <v>1.154660557272061</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>65.04756953651888</v>
+        <v>54.20630794709907</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1575487105448568</v>
+        <v>0.1571831046805298</v>
       </c>
       <c r="C8">
-        <v>2208.056951283723</v>
+        <v>2192.352085951954</v>
       </c>
       <c r="D8">
-        <v>2206.950951283723</v>
+        <v>2214.195085951954</v>
       </c>
       <c r="E8">
-        <v>-1481.006</v>
+        <v>-1458.057</v>
       </c>
       <c r="F8">
-        <v>137.694</v>
+        <v>160.643</v>
       </c>
       <c r="G8">
         <v>138.8</v>
@@ -1931,28 +1931,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M8">
-        <v>6.926008199999999</v>
+        <v>8.0803429</v>
       </c>
       <c r="N8">
-        <v>368.5073251333333</v>
+        <v>367.3529904333333</v>
       </c>
       <c r="O8">
-        <v>92.12683128333333</v>
+        <v>91.83824760833333</v>
       </c>
       <c r="P8">
-        <v>276.38049385</v>
+        <v>275.514742825</v>
       </c>
       <c r="Q8">
-        <v>358.28049385</v>
+        <v>357.414742825</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1651970324945285</v>
+        <v>0.1661745749253008</v>
       </c>
       <c r="T8">
-        <v>1.154660557272061</v>
+        <v>1.164114139696099</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>54.20630794709908</v>
+        <v>46.46254966894206</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1571831046805298</v>
+        <v>0.1568174988162027</v>
       </c>
       <c r="C9">
-        <v>2192.352085951954</v>
+        <v>2176.694933785136</v>
       </c>
       <c r="D9">
-        <v>2214.195085951954</v>
+        <v>2221.486933785136</v>
       </c>
       <c r="E9">
-        <v>-1458.057</v>
+        <v>-1435.108</v>
       </c>
       <c r="F9">
-        <v>160.643</v>
+        <v>183.592</v>
       </c>
       <c r="G9">
         <v>138.8</v>
@@ -2013,28 +2013,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M9">
-        <v>8.080342900000002</v>
+        <v>9.234677599999999</v>
       </c>
       <c r="N9">
-        <v>367.3529904333333</v>
+        <v>366.1986557333333</v>
       </c>
       <c r="O9">
-        <v>91.83824760833333</v>
+        <v>91.54966393333333</v>
       </c>
       <c r="P9">
-        <v>275.514742825</v>
+        <v>274.6489918</v>
       </c>
       <c r="Q9">
-        <v>357.414742825</v>
+        <v>356.5489918</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1661745749253008</v>
+        <v>0.1671733682784812</v>
       </c>
       <c r="T9">
-        <v>1.164114139696099</v>
+        <v>1.17377323478153</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>46.46254966894205</v>
+        <v>40.65473096032431</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1568174988162027</v>
+        <v>0.1564518929518757</v>
       </c>
       <c r="C10">
-        <v>2176.694933785136</v>
+        <v>2161.085967731695</v>
       </c>
       <c r="D10">
-        <v>2221.486933785136</v>
+        <v>2228.826967731695</v>
       </c>
       <c r="E10">
-        <v>-1435.108</v>
+        <v>-1412.159</v>
       </c>
       <c r="F10">
-        <v>183.592</v>
+        <v>206.541</v>
       </c>
       <c r="G10">
         <v>138.8</v>
@@ -2095,28 +2095,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M10">
-        <v>9.234677599999999</v>
+        <v>10.3890123</v>
       </c>
       <c r="N10">
-        <v>366.1986557333333</v>
+        <v>365.0443210333333</v>
       </c>
       <c r="O10">
-        <v>91.54966393333333</v>
+        <v>91.26108025833334</v>
       </c>
       <c r="P10">
-        <v>274.6489918</v>
+        <v>273.783240775</v>
       </c>
       <c r="Q10">
-        <v>356.5489918</v>
+        <v>355.683240775</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1671733682784812</v>
+        <v>0.1681941131339293</v>
       </c>
       <c r="T10">
-        <v>1.17377323478153</v>
+        <v>1.183644617671036</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>40.65473096032431</v>
+        <v>36.13753863139939</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1564518929518757</v>
+        <v>0.1560862870875486</v>
       </c>
       <c r="C11">
-        <v>2161.085967731695</v>
+        <v>2145.525667011471</v>
       </c>
       <c r="D11">
-        <v>2228.826967731695</v>
+        <v>2236.215667011471</v>
       </c>
       <c r="E11">
-        <v>-1412.159</v>
+        <v>-1389.21</v>
       </c>
       <c r="F11">
-        <v>206.541</v>
+        <v>229.49</v>
       </c>
       <c r="G11">
         <v>138.8</v>
@@ -2177,28 +2177,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M11">
-        <v>10.3890123</v>
+        <v>11.543347</v>
       </c>
       <c r="N11">
-        <v>365.0443210333333</v>
+        <v>363.8899863333334</v>
       </c>
       <c r="O11">
-        <v>91.26108025833334</v>
+        <v>90.97249658333334</v>
       </c>
       <c r="P11">
-        <v>273.783240775</v>
+        <v>272.91748975</v>
       </c>
       <c r="Q11">
-        <v>355.683240775</v>
+        <v>354.81748975</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1681941131339293</v>
+        <v>0.1692375412083874</v>
       </c>
       <c r="T11">
-        <v>1.183644617671036</v>
+        <v>1.193735364624753</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>36.13753863139939</v>
+        <v>32.52378476825945</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1560862870875486</v>
+        <v>0.1557206812232216</v>
       </c>
       <c r="C12">
-        <v>2145.525667011471</v>
+        <v>2130.014517220015</v>
       </c>
       <c r="D12">
-        <v>2236.215667011471</v>
+        <v>2243.653517220014</v>
       </c>
       <c r="E12">
-        <v>-1389.21</v>
+        <v>-1366.261</v>
       </c>
       <c r="F12">
-        <v>229.49</v>
+        <v>252.439</v>
       </c>
       <c r="G12">
         <v>138.8</v>
@@ -2259,28 +2259,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M12">
-        <v>11.543347</v>
+        <v>12.6976817</v>
       </c>
       <c r="N12">
-        <v>363.8899863333334</v>
+        <v>362.7356516333334</v>
       </c>
       <c r="O12">
-        <v>90.97249658333334</v>
+        <v>90.68391290833334</v>
       </c>
       <c r="P12">
-        <v>272.91748975</v>
+        <v>272.051738725</v>
       </c>
       <c r="Q12">
-        <v>354.81748975</v>
+        <v>353.951738725</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1692375412083874</v>
+        <v>0.1703044171047434</v>
       </c>
       <c r="T12">
-        <v>1.193735364624753</v>
+        <v>1.204052869936981</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>32.52378476825945</v>
+        <v>29.56707706205404</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1557206812232216</v>
+        <v>0.1553550753588946</v>
       </c>
       <c r="C13">
-        <v>2130.014517220015</v>
+        <v>2114.55301043497</v>
       </c>
       <c r="D13">
-        <v>2243.653517220014</v>
+        <v>2251.141010434969</v>
       </c>
       <c r="E13">
-        <v>-1366.261</v>
+        <v>-1343.312</v>
       </c>
       <c r="F13">
-        <v>252.439</v>
+        <v>275.388</v>
       </c>
       <c r="G13">
         <v>138.8</v>
@@ -2341,28 +2341,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M13">
-        <v>12.6976817</v>
+        <v>13.8520164</v>
       </c>
       <c r="N13">
-        <v>362.7356516333334</v>
+        <v>361.5813169333333</v>
       </c>
       <c r="O13">
-        <v>90.68391290833334</v>
+        <v>90.39532923333333</v>
       </c>
       <c r="P13">
-        <v>272.051738725</v>
+        <v>271.1859877</v>
       </c>
       <c r="Q13">
-        <v>353.951738725</v>
+        <v>353.0859877</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1703044171047434</v>
+        <v>0.171395540180562</v>
       </c>
       <c r="T13">
-        <v>1.204052869936981</v>
+        <v>1.214604864006305</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>29.56707706205404</v>
+        <v>27.10315397354954</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1553550753588946</v>
+        <v>0.1549894694945675</v>
       </c>
       <c r="C14">
-        <v>2114.55301043497</v>
+        <v>2099.141645324597</v>
       </c>
       <c r="D14">
-        <v>2251.141010434969</v>
+        <v>2258.678645324597</v>
       </c>
       <c r="E14">
-        <v>-1343.312</v>
+        <v>-1320.363</v>
       </c>
       <c r="F14">
-        <v>275.388</v>
+        <v>298.337</v>
       </c>
       <c r="G14">
         <v>138.8</v>
@@ -2423,28 +2423,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M14">
-        <v>13.8520164</v>
+        <v>15.0063511</v>
       </c>
       <c r="N14">
-        <v>361.5813169333333</v>
+        <v>360.4269822333333</v>
       </c>
       <c r="O14">
-        <v>90.39532923333333</v>
+        <v>90.10674555833333</v>
       </c>
       <c r="P14">
-        <v>271.1859877</v>
+        <v>270.320236675</v>
       </c>
       <c r="Q14">
-        <v>353.0859877</v>
+        <v>352.220236675</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.171395540180562</v>
+        <v>0.1725117465454799</v>
       </c>
       <c r="T14">
-        <v>1.214604864006305</v>
+        <v>1.225399432651935</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>27.10315397354954</v>
+        <v>25.01829597558418</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1549894694945675</v>
+        <v>0.1546238636302404</v>
       </c>
       <c r="C15">
-        <v>2099.141645324597</v>
+        <v>2083.780927258482</v>
       </c>
       <c r="D15">
-        <v>2258.678645324597</v>
+        <v>2266.266927258482</v>
       </c>
       <c r="E15">
-        <v>-1320.363</v>
+        <v>-1297.414</v>
       </c>
       <c r="F15">
-        <v>298.337</v>
+        <v>321.2860000000001</v>
       </c>
       <c r="G15">
         <v>138.8</v>
@@ -2505,28 +2505,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M15">
-        <v>15.0063511</v>
+        <v>16.1606858</v>
       </c>
       <c r="N15">
-        <v>360.4269822333333</v>
+        <v>359.2726475333333</v>
       </c>
       <c r="O15">
-        <v>90.10674555833333</v>
+        <v>89.81816188333333</v>
       </c>
       <c r="P15">
-        <v>270.320236675</v>
+        <v>269.45448565</v>
       </c>
       <c r="Q15">
-        <v>352.220236675</v>
+        <v>351.35448565</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1725117465454799</v>
+        <v>0.173653911197954</v>
       </c>
       <c r="T15">
-        <v>1.225399432651935</v>
+        <v>1.236445037777696</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>25.01829597558418</v>
+        <v>23.23127483447103</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1546238636302404</v>
+        <v>0.1542582577659134</v>
       </c>
       <c r="C16">
-        <v>2083.780927258482</v>
+        <v>2068.471368420487</v>
       </c>
       <c r="D16">
-        <v>2266.266927258482</v>
+        <v>2273.906368420487</v>
       </c>
       <c r="E16">
-        <v>-1297.414</v>
+        <v>-1274.465</v>
       </c>
       <c r="F16">
-        <v>321.2860000000001</v>
+        <v>344.2350000000001</v>
       </c>
       <c r="G16">
         <v>138.8</v>
@@ -2587,28 +2587,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M16">
-        <v>16.1606858</v>
+        <v>17.3150205</v>
       </c>
       <c r="N16">
-        <v>359.2726475333333</v>
+        <v>358.1183128333333</v>
       </c>
       <c r="O16">
-        <v>89.81816188333333</v>
+        <v>89.52957820833333</v>
       </c>
       <c r="P16">
-        <v>269.45448565</v>
+        <v>268.588734625</v>
       </c>
       <c r="Q16">
-        <v>351.35448565</v>
+        <v>350.488734625</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.173653911197954</v>
+        <v>0.1748229503128393</v>
       </c>
       <c r="T16">
-        <v>1.236445037777696</v>
+        <v>1.247750539494652</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>23.23127483447103</v>
+        <v>21.68252317883962</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1542582577659134</v>
+        <v>0.1538926519015864</v>
       </c>
       <c r="C17">
-        <v>2068.471368420487</v>
+        <v>2053.213487923985</v>
       </c>
       <c r="D17">
-        <v>2273.906368420487</v>
+        <v>2281.597487923985</v>
       </c>
       <c r="E17">
-        <v>-1274.465</v>
+        <v>-1251.516</v>
       </c>
       <c r="F17">
-        <v>344.235</v>
+        <v>367.184</v>
       </c>
       <c r="G17">
         <v>138.8</v>
@@ -2669,28 +2669,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M17">
-        <v>17.3150205</v>
+        <v>18.4693552</v>
       </c>
       <c r="N17">
-        <v>358.1183128333333</v>
+        <v>356.9639781333333</v>
       </c>
       <c r="O17">
-        <v>89.52957820833333</v>
+        <v>89.24099453333334</v>
       </c>
       <c r="P17">
-        <v>268.588734625</v>
+        <v>267.7229836</v>
       </c>
       <c r="Q17">
-        <v>350.488734625</v>
+        <v>349.6229836</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1748229503128393</v>
+        <v>0.1760198236923647</v>
       </c>
       <c r="T17">
-        <v>1.247750539494652</v>
+        <v>1.259325219823915</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>21.68252317883963</v>
+        <v>20.32736548016215</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1538926519015864</v>
+        <v>0.1535270460372593</v>
       </c>
       <c r="C18">
-        <v>2053.213487923985</v>
+        <v>2038.007811929456</v>
       </c>
       <c r="D18">
-        <v>2281.597487923985</v>
+        <v>2289.340811929456</v>
       </c>
       <c r="E18">
-        <v>-1251.516</v>
+        <v>-1228.567</v>
       </c>
       <c r="F18">
-        <v>367.184</v>
+        <v>390.133</v>
       </c>
       <c r="G18">
         <v>138.8</v>
@@ -2751,28 +2751,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M18">
-        <v>18.4693552</v>
+        <v>19.6236899</v>
       </c>
       <c r="N18">
-        <v>356.9639781333333</v>
+        <v>355.8096434333333</v>
       </c>
       <c r="O18">
-        <v>89.24099453333334</v>
+        <v>88.95241085833334</v>
       </c>
       <c r="P18">
-        <v>267.7229836</v>
+        <v>266.857232575</v>
       </c>
       <c r="Q18">
-        <v>349.6229836</v>
+        <v>348.757232575</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1760198236923647</v>
+        <v>0.1772455373942883</v>
       </c>
       <c r="T18">
-        <v>1.259325219823915</v>
+        <v>1.271178808112921</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>20.32736548016215</v>
+        <v>19.13163809897614</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1535270460372593</v>
+        <v>0.1531614401729323</v>
       </c>
       <c r="C19">
-        <v>2038.007811929456</v>
+        <v>2022.854873764473</v>
       </c>
       <c r="D19">
-        <v>2289.340811929456</v>
+        <v>2297.136873764473</v>
       </c>
       <c r="E19">
-        <v>-1228.567</v>
+        <v>-1205.618</v>
       </c>
       <c r="F19">
-        <v>390.133</v>
+        <v>413.0820000000001</v>
       </c>
       <c r="G19">
         <v>138.8</v>
@@ -2833,28 +2833,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M19">
-        <v>19.6236899</v>
+        <v>20.7780246</v>
       </c>
       <c r="N19">
-        <v>355.8096434333333</v>
+        <v>354.6553087333334</v>
       </c>
       <c r="O19">
-        <v>88.95241085833334</v>
+        <v>88.66382718333334</v>
       </c>
       <c r="P19">
-        <v>266.857232575</v>
+        <v>265.99148155</v>
       </c>
       <c r="Q19">
-        <v>348.757232575</v>
+        <v>347.89148155</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1772455373942883</v>
+        <v>0.1785011465523564</v>
       </c>
       <c r="T19">
-        <v>1.271178808112921</v>
+        <v>1.283321508311414</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>19.13163809897614</v>
+        <v>18.06876931569969</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1531614401729323</v>
+        <v>0.1527958343086052</v>
       </c>
       <c r="C20">
-        <v>2022.854873764474</v>
+        <v>2007.75521404615</v>
       </c>
       <c r="D20">
-        <v>2297.136873764473</v>
+        <v>2304.98621404615</v>
       </c>
       <c r="E20">
-        <v>-1205.618</v>
+        <v>-1182.669</v>
       </c>
       <c r="F20">
-        <v>413.082</v>
+        <v>436.031</v>
       </c>
       <c r="G20">
         <v>138.8</v>
@@ -2915,28 +2915,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M20">
-        <v>20.7780246</v>
+        <v>21.9323593</v>
       </c>
       <c r="N20">
-        <v>354.6553087333334</v>
+        <v>353.5009740333334</v>
       </c>
       <c r="O20">
-        <v>88.66382718333334</v>
+        <v>88.37524350833334</v>
       </c>
       <c r="P20">
-        <v>265.99148155</v>
+        <v>265.125730525</v>
       </c>
       <c r="Q20">
-        <v>347.89148155</v>
+        <v>347.025730525</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1785011465523564</v>
+        <v>0.1797877584056854</v>
       </c>
       <c r="T20">
-        <v>1.283321508311414</v>
+        <v>1.295764028267895</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>18.06876931569969</v>
+        <v>17.11778145697866</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1527958343086052</v>
+        <v>0.1524302284442782</v>
       </c>
       <c r="C21">
-        <v>2007.75521404615</v>
+        <v>1992.709380806115</v>
       </c>
       <c r="D21">
-        <v>2304.98621404615</v>
+        <v>2312.889380806115</v>
       </c>
       <c r="E21">
-        <v>-1182.669</v>
+        <v>-1159.72</v>
       </c>
       <c r="F21">
-        <v>436.031</v>
+        <v>458.98</v>
       </c>
       <c r="G21">
         <v>138.8</v>
@@ -2997,28 +2997,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M21">
-        <v>21.9323593</v>
+        <v>23.086694</v>
       </c>
       <c r="N21">
-        <v>353.5009740333334</v>
+        <v>352.3466393333333</v>
       </c>
       <c r="O21">
-        <v>88.37524350833334</v>
+        <v>88.08665983333333</v>
       </c>
       <c r="P21">
-        <v>265.125730525</v>
+        <v>264.2599795</v>
       </c>
       <c r="Q21">
-        <v>347.025730525</v>
+        <v>346.1599795</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1797877584056854</v>
+        <v>0.1811065355553477</v>
       </c>
       <c r="T21">
-        <v>1.295764028267895</v>
+        <v>1.308517611223287</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>17.11778145697866</v>
+        <v>16.26189238412972</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1524302284442782</v>
+        <v>0.1520646225799511</v>
       </c>
       <c r="C22">
-        <v>1992.709380806115</v>
+        <v>1977.717929618057</v>
       </c>
       <c r="D22">
-        <v>2312.889380806115</v>
+        <v>2320.846929618056</v>
       </c>
       <c r="E22">
-        <v>-1159.72</v>
+        <v>-1136.771</v>
       </c>
       <c r="F22">
-        <v>458.98</v>
+        <v>481.9290000000001</v>
       </c>
       <c r="G22">
         <v>138.8</v>
@@ -3079,28 +3079,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M22">
-        <v>23.086694</v>
+        <v>24.2410287</v>
       </c>
       <c r="N22">
-        <v>352.3466393333333</v>
+        <v>351.1923046333333</v>
       </c>
       <c r="O22">
-        <v>88.08665983333333</v>
+        <v>87.79807615833333</v>
       </c>
       <c r="P22">
-        <v>264.2599795</v>
+        <v>263.394228475</v>
       </c>
       <c r="Q22">
-        <v>346.1599795</v>
+        <v>345.294228475</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1811065355553477</v>
+        <v>0.1824586994682925</v>
       </c>
       <c r="T22">
-        <v>1.308517611223287</v>
+        <v>1.321594069696538</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>16.26189238412972</v>
+        <v>15.48751655631402</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1520646225799511</v>
+        <v>0.1516990167156241</v>
       </c>
       <c r="C23">
-        <v>1977.717929618057</v>
+        <v>1962.781423727915</v>
       </c>
       <c r="D23">
-        <v>2320.846929618056</v>
+        <v>2328.859423727915</v>
       </c>
       <c r="E23">
-        <v>-1136.771</v>
+        <v>-1113.822</v>
       </c>
       <c r="F23">
-        <v>481.929</v>
+        <v>504.878</v>
       </c>
       <c r="G23">
         <v>138.8</v>
@@ -3161,28 +3161,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M23">
-        <v>24.2410287</v>
+        <v>25.3953634</v>
       </c>
       <c r="N23">
-        <v>351.1923046333333</v>
+        <v>350.0379699333333</v>
       </c>
       <c r="O23">
-        <v>87.79807615833333</v>
+        <v>87.50949248333333</v>
       </c>
       <c r="P23">
-        <v>263.394228475</v>
+        <v>262.52847745</v>
       </c>
       <c r="Q23">
-        <v>345.294228475</v>
+        <v>344.4284774499999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1824586994682925</v>
+        <v>0.1838455342508001</v>
       </c>
       <c r="T23">
-        <v>1.321594069696538</v>
+        <v>1.335005821976795</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>15.48751655631402</v>
+        <v>14.78353853102702</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1516990167156241</v>
+        <v>0.151333410851297</v>
       </c>
       <c r="C24">
-        <v>1962.781423727915</v>
+        <v>1947.900434186783</v>
       </c>
       <c r="D24">
-        <v>2328.859423727915</v>
+        <v>2336.927434186783</v>
       </c>
       <c r="E24">
-        <v>-1113.822</v>
+        <v>-1090.873</v>
       </c>
       <c r="F24">
-        <v>504.878</v>
+        <v>527.827</v>
       </c>
       <c r="G24">
         <v>138.8</v>
@@ -3243,28 +3243,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M24">
-        <v>25.3953634</v>
+        <v>26.5496981</v>
       </c>
       <c r="N24">
-        <v>350.0379699333333</v>
+        <v>348.8836352333333</v>
       </c>
       <c r="O24">
-        <v>87.50949248333333</v>
+        <v>87.22090880833333</v>
       </c>
       <c r="P24">
-        <v>262.52847745</v>
+        <v>261.662726425</v>
       </c>
       <c r="Q24">
-        <v>344.4284774499999</v>
+        <v>343.562726425</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1838455342508001</v>
+        <v>0.1852683907159701</v>
       </c>
       <c r="T24">
-        <v>1.335005821976795</v>
+        <v>1.348765931459137</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>14.78353853102702</v>
+        <v>14.14077598619976</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.151333410851297</v>
+        <v>0.15096780498697</v>
       </c>
       <c r="C25">
-        <v>1947.900434186783</v>
+        <v>1933.075539986569</v>
       </c>
       <c r="D25">
-        <v>2336.927434186783</v>
+        <v>2345.051539986569</v>
       </c>
       <c r="E25">
-        <v>-1090.873</v>
+        <v>-1067.924</v>
       </c>
       <c r="F25">
-        <v>527.827</v>
+        <v>550.7760000000001</v>
       </c>
       <c r="G25">
         <v>138.8</v>
@@ -3325,28 +3325,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M25">
-        <v>26.5496981</v>
+        <v>27.7040328</v>
       </c>
       <c r="N25">
-        <v>348.8836352333333</v>
+        <v>347.7293005333333</v>
       </c>
       <c r="O25">
-        <v>87.22090880833333</v>
+        <v>86.93232513333334</v>
       </c>
       <c r="P25">
-        <v>261.662726425</v>
+        <v>260.7969754</v>
       </c>
       <c r="Q25">
-        <v>343.562726425</v>
+        <v>342.6969754</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1852683907159701</v>
+        <v>0.1867286907723289</v>
       </c>
       <c r="T25">
-        <v>1.348765931459137</v>
+        <v>1.362888149085751</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>14.14077598619976</v>
+        <v>13.55157698677477</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.15096780498697</v>
+        <v>0.1506021991226429</v>
       </c>
       <c r="C26">
-        <v>1933.075539986569</v>
+        <v>1918.307328198513</v>
       </c>
       <c r="D26">
-        <v>2345.051539986569</v>
+        <v>2353.232328198513</v>
       </c>
       <c r="E26">
-        <v>-1067.924</v>
+        <v>-1044.975</v>
       </c>
       <c r="F26">
-        <v>550.776</v>
+        <v>573.725</v>
       </c>
       <c r="G26">
         <v>138.8</v>
@@ -3407,28 +3407,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M26">
-        <v>27.7040328</v>
+        <v>28.8583675</v>
       </c>
       <c r="N26">
-        <v>347.7293005333333</v>
+        <v>346.5749658333334</v>
       </c>
       <c r="O26">
-        <v>86.93232513333334</v>
+        <v>86.64374145833334</v>
       </c>
       <c r="P26">
-        <v>260.7969754</v>
+        <v>259.931224375</v>
       </c>
       <c r="Q26">
-        <v>342.6969754</v>
+        <v>341.831224375</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1867286907723289</v>
+        <v>0.1882279321635239</v>
       </c>
       <c r="T26">
-        <v>1.362888149085751</v>
+        <v>1.377386959182407</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>13.55157698677477</v>
+        <v>13.00951390730378</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1506021991226429</v>
+        <v>0.1505290932583159</v>
       </c>
       <c r="C27">
-        <v>1918.307328198513</v>
+        <v>1897.000995751177</v>
       </c>
       <c r="D27">
-        <v>2353.232328198513</v>
+        <v>2354.874995751176</v>
       </c>
       <c r="E27">
-        <v>-1044.975</v>
+        <v>-1022.026</v>
       </c>
       <c r="F27">
-        <v>573.725</v>
+        <v>596.6740000000001</v>
       </c>
       <c r="G27">
         <v>138.8</v>
@@ -3489,45 +3489,45 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M27">
-        <v>28.8583675</v>
+        <v>30.9077132</v>
       </c>
       <c r="N27">
-        <v>346.5749658333334</v>
+        <v>344.5256201333333</v>
       </c>
       <c r="O27">
-        <v>86.64374145833334</v>
+        <v>86.13140503333334</v>
       </c>
       <c r="P27">
-        <v>259.931224375</v>
+        <v>258.3942151</v>
       </c>
       <c r="Q27">
-        <v>341.831224375</v>
+        <v>340.2942151</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1882279321635239</v>
+        <v>0.1897676935923188</v>
       </c>
       <c r="T27">
-        <v>1.377386959182407</v>
+        <v>1.392277629011407</v>
       </c>
       <c r="U27">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V27">
         <v>0.25</v>
       </c>
       <c r="W27">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y27">
-        <v>13.00951390730378</v>
+        <v>12.14691397270159</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1505290932583159</v>
+        <v>0.1501747373939888</v>
       </c>
       <c r="C28">
-        <v>1897.000995751177</v>
+        <v>1882.046878280573</v>
       </c>
       <c r="D28">
-        <v>2354.874995751176</v>
+        <v>2362.869878280573</v>
       </c>
       <c r="E28">
-        <v>-1022.026</v>
+        <v>-999.077</v>
       </c>
       <c r="F28">
-        <v>596.6740000000001</v>
+        <v>619.623</v>
       </c>
       <c r="G28">
         <v>138.8</v>
@@ -3571,28 +3571,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M28">
-        <v>30.9077132</v>
+        <v>32.0964714</v>
       </c>
       <c r="N28">
-        <v>344.5256201333333</v>
+        <v>343.3368619333334</v>
       </c>
       <c r="O28">
-        <v>86.13140503333334</v>
+        <v>85.83421548333334</v>
       </c>
       <c r="P28">
-        <v>258.3942151</v>
+        <v>257.50264645</v>
       </c>
       <c r="Q28">
-        <v>340.2942151</v>
+        <v>339.40264645</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1897676935923188</v>
+        <v>0.1913496402657381</v>
       </c>
       <c r="T28">
-        <v>1.392277629011407</v>
+        <v>1.407576262397365</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>12.14691397270159</v>
+        <v>11.69702827000894</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1501747373939888</v>
+        <v>0.1498203815296618</v>
       </c>
       <c r="C29">
-        <v>1882.046878280573</v>
+        <v>1867.147231548631</v>
       </c>
       <c r="D29">
-        <v>2362.869878280573</v>
+        <v>2370.919231548631</v>
       </c>
       <c r="E29">
-        <v>-999.077</v>
+        <v>-976.1279999999999</v>
       </c>
       <c r="F29">
-        <v>619.623</v>
+        <v>642.5720000000001</v>
       </c>
       <c r="G29">
         <v>138.8</v>
@@ -3653,28 +3653,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M29">
-        <v>32.0964714</v>
+        <v>33.28522960000001</v>
       </c>
       <c r="N29">
-        <v>343.3368619333334</v>
+        <v>342.1481037333333</v>
       </c>
       <c r="O29">
-        <v>85.83421548333334</v>
+        <v>85.53702593333333</v>
       </c>
       <c r="P29">
-        <v>257.50264645</v>
+        <v>256.6110778</v>
       </c>
       <c r="Q29">
-        <v>339.40264645</v>
+        <v>338.5110778</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1913496402657381</v>
+        <v>0.192975529902308</v>
       </c>
       <c r="T29">
-        <v>1.407576262397365</v>
+        <v>1.423299857821821</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>11.69702827000894</v>
+        <v>11.27927726036576</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1498203815296618</v>
+        <v>0.1494660256653347</v>
       </c>
       <c r="C30">
-        <v>1867.147231548631</v>
+        <v>1852.302614138326</v>
       </c>
       <c r="D30">
-        <v>2370.919231548631</v>
+        <v>2379.023614138326</v>
       </c>
       <c r="E30">
-        <v>-976.1279999999999</v>
+        <v>-953.179</v>
       </c>
       <c r="F30">
-        <v>642.5720000000001</v>
+        <v>665.5210000000001</v>
       </c>
       <c r="G30">
         <v>138.8</v>
@@ -3735,28 +3735,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M30">
-        <v>33.28522960000001</v>
+        <v>34.4739878</v>
       </c>
       <c r="N30">
-        <v>342.1481037333333</v>
+        <v>340.9593455333334</v>
       </c>
       <c r="O30">
-        <v>85.53702593333333</v>
+        <v>85.23983638333334</v>
       </c>
       <c r="P30">
-        <v>256.6110778</v>
+        <v>255.71950915</v>
       </c>
       <c r="Q30">
-        <v>338.5110778</v>
+        <v>337.61950915</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.192975529902308</v>
+        <v>0.1946472192469503</v>
       </c>
       <c r="T30">
-        <v>1.423299857821821</v>
+        <v>1.439466371427248</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>11.27927726036576</v>
+        <v>10.89033666518073</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1494660256653347</v>
+        <v>0.1491116698010077</v>
       </c>
       <c r="C31">
-        <v>1852.302614138326</v>
+        <v>1837.513592296325</v>
       </c>
       <c r="D31">
-        <v>2379.023614138326</v>
+        <v>2387.183592296325</v>
       </c>
       <c r="E31">
-        <v>-953.1790000000001</v>
+        <v>-930.23</v>
       </c>
       <c r="F31">
-        <v>665.521</v>
+        <v>688.47</v>
       </c>
       <c r="G31">
         <v>138.8</v>
@@ -3817,28 +3817,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M31">
-        <v>34.4739878</v>
+        <v>35.662746</v>
       </c>
       <c r="N31">
-        <v>340.9593455333334</v>
+        <v>339.7705873333333</v>
       </c>
       <c r="O31">
-        <v>85.23983638333334</v>
+        <v>84.94264683333333</v>
       </c>
       <c r="P31">
-        <v>255.71950915</v>
+        <v>254.8279405</v>
       </c>
       <c r="Q31">
-        <v>337.61950915</v>
+        <v>336.7279404999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1946472192469503</v>
+        <v>0.1963666711442967</v>
       </c>
       <c r="T31">
-        <v>1.439466371427248</v>
+        <v>1.456094785421402</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>10.89033666518074</v>
+        <v>10.52732544300804</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1491116698010077</v>
+        <v>0.1487573139366806</v>
       </c>
       <c r="C32">
-        <v>1837.513592296325</v>
+        <v>1822.780740064862</v>
       </c>
       <c r="D32">
-        <v>2387.183592296325</v>
+        <v>2395.399740064862</v>
       </c>
       <c r="E32">
-        <v>-930.23</v>
+        <v>-907.2810000000001</v>
       </c>
       <c r="F32">
-        <v>688.47</v>
+        <v>711.419</v>
       </c>
       <c r="G32">
         <v>138.8</v>
@@ -3899,28 +3899,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M32">
-        <v>35.662746</v>
+        <v>36.8515042</v>
       </c>
       <c r="N32">
-        <v>339.7705873333333</v>
+        <v>338.5818291333333</v>
       </c>
       <c r="O32">
-        <v>84.94264683333333</v>
+        <v>84.64545728333333</v>
       </c>
       <c r="P32">
-        <v>254.8279405</v>
+        <v>253.93637185</v>
       </c>
       <c r="Q32">
-        <v>336.7279404999999</v>
+        <v>335.83637185</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1963666711442967</v>
+        <v>0.1981359622270734</v>
       </c>
       <c r="T32">
-        <v>1.456094785421402</v>
+        <v>1.473205182429879</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>10.52732544300804</v>
+        <v>10.1877342996852</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1487573139366806</v>
+        <v>0.1484029580723536</v>
       </c>
       <c r="C33">
-        <v>1822.780740064862</v>
+        <v>1808.104639416369</v>
       </c>
       <c r="D33">
-        <v>2395.399740064862</v>
+        <v>2403.672639416369</v>
       </c>
       <c r="E33">
-        <v>-907.2810000000001</v>
+        <v>-884.332</v>
       </c>
       <c r="F33">
-        <v>711.419</v>
+        <v>734.3680000000001</v>
       </c>
       <c r="G33">
         <v>138.8</v>
@@ -3981,28 +3981,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M33">
-        <v>36.8515042</v>
+        <v>38.0402624</v>
       </c>
       <c r="N33">
-        <v>338.5818291333333</v>
+        <v>337.3930709333333</v>
       </c>
       <c r="O33">
-        <v>84.64545728333333</v>
+        <v>84.34826773333333</v>
       </c>
       <c r="P33">
-        <v>253.93637185</v>
+        <v>253.0448032</v>
       </c>
       <c r="Q33">
-        <v>335.83637185</v>
+        <v>334.9448032</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1981359622270734</v>
+        <v>0.1999572912828729</v>
       </c>
       <c r="T33">
-        <v>1.473205182429879</v>
+        <v>1.490818826409194</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>10.1877342996852</v>
+        <v>9.86936760282004</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1484029580723536</v>
+        <v>0.1484693522080266</v>
       </c>
       <c r="C34">
-        <v>1808.104639416369</v>
+        <v>1783.601234290568</v>
       </c>
       <c r="D34">
-        <v>2403.672639416369</v>
+        <v>2402.118234290568</v>
       </c>
       <c r="E34">
-        <v>-884.332</v>
+        <v>-861.3829999999999</v>
       </c>
       <c r="F34">
-        <v>734.3680000000001</v>
+        <v>757.3170000000001</v>
       </c>
       <c r="G34">
         <v>138.8</v>
@@ -4063,45 +4063,45 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M34">
-        <v>38.0402624</v>
+        <v>40.5164595</v>
       </c>
       <c r="N34">
-        <v>337.3930709333333</v>
+        <v>334.9168738333333</v>
       </c>
       <c r="O34">
-        <v>84.34826773333333</v>
+        <v>83.72921845833334</v>
       </c>
       <c r="P34">
-        <v>253.0448032</v>
+        <v>251.187655375</v>
       </c>
       <c r="Q34">
-        <v>334.9448032</v>
+        <v>333.087655375</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1999572912828729</v>
+        <v>0.2018329883701889</v>
       </c>
       <c r="T34">
-        <v>1.490818826409194</v>
+        <v>1.508958250805802</v>
       </c>
       <c r="U34">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V34">
         <v>0.25</v>
       </c>
       <c r="W34">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>9.86936760282004</v>
+        <v>9.266192998263664</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1484693522080266</v>
+        <v>0.1481277463436995</v>
       </c>
       <c r="C35">
-        <v>1783.601234290568</v>
+        <v>1768.671346456729</v>
       </c>
       <c r="D35">
-        <v>2402.118234290568</v>
+        <v>2410.137346456729</v>
       </c>
       <c r="E35">
-        <v>-861.3829999999999</v>
+        <v>-838.434</v>
       </c>
       <c r="F35">
-        <v>757.3170000000001</v>
+        <v>780.2660000000001</v>
       </c>
       <c r="G35">
         <v>138.8</v>
@@ -4145,28 +4145,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M35">
-        <v>40.5164595</v>
+        <v>41.74423100000001</v>
       </c>
       <c r="N35">
-        <v>334.9168738333333</v>
+        <v>333.6891023333333</v>
       </c>
       <c r="O35">
-        <v>83.72921845833334</v>
+        <v>83.42227558333333</v>
       </c>
       <c r="P35">
-        <v>251.187655375</v>
+        <v>250.26682675</v>
       </c>
       <c r="Q35">
-        <v>333.087655375</v>
+        <v>332.16682675</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2018329883701889</v>
+        <v>0.2037655247631811</v>
       </c>
       <c r="T35">
-        <v>1.508958250805802</v>
+        <v>1.527647354729579</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>9.266192998263664</v>
+        <v>8.993657910079438</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1481277463436995</v>
+        <v>0.1477861404793724</v>
       </c>
       <c r="C36">
-        <v>1768.671346456729</v>
+        <v>1753.795179172168</v>
       </c>
       <c r="D36">
-        <v>2410.137346456729</v>
+        <v>2418.210179172168</v>
       </c>
       <c r="E36">
-        <v>-838.434</v>
+        <v>-815.4849999999999</v>
       </c>
       <c r="F36">
-        <v>780.2660000000001</v>
+        <v>803.2150000000001</v>
       </c>
       <c r="G36">
         <v>138.8</v>
@@ -4227,28 +4227,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M36">
-        <v>41.74423100000001</v>
+        <v>42.97200250000001</v>
       </c>
       <c r="N36">
-        <v>333.6891023333333</v>
+        <v>332.4613308333333</v>
       </c>
       <c r="O36">
-        <v>83.42227558333333</v>
+        <v>83.11533270833333</v>
       </c>
       <c r="P36">
-        <v>250.26682675</v>
+        <v>249.345998125</v>
       </c>
       <c r="Q36">
-        <v>332.16682675</v>
+        <v>331.245998125</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2037655247631811</v>
+        <v>0.2057575238144192</v>
       </c>
       <c r="T36">
-        <v>1.527647354729579</v>
+        <v>1.546911508004858</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.993657910079438</v>
+        <v>8.736696255505738</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1477861404793724</v>
+        <v>0.1474445346150454</v>
       </c>
       <c r="C37">
-        <v>1753.795179172168</v>
+        <v>1738.973274067227</v>
       </c>
       <c r="D37">
-        <v>2418.210179172168</v>
+        <v>2426.337274067227</v>
       </c>
       <c r="E37">
-        <v>-815.4849999999999</v>
+        <v>-792.5359999999999</v>
       </c>
       <c r="F37">
-        <v>803.2150000000001</v>
+        <v>826.1640000000001</v>
       </c>
       <c r="G37">
         <v>138.8</v>
@@ -4309,28 +4309,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M37">
-        <v>42.97200250000001</v>
+        <v>44.19977400000001</v>
       </c>
       <c r="N37">
-        <v>332.4613308333333</v>
+        <v>331.2335593333333</v>
       </c>
       <c r="O37">
-        <v>83.11533270833333</v>
+        <v>82.80838983333334</v>
       </c>
       <c r="P37">
-        <v>249.345998125</v>
+        <v>248.4251695</v>
       </c>
       <c r="Q37">
-        <v>331.245998125</v>
+        <v>330.3251695</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2057575238144192</v>
+        <v>0.2078117728360084</v>
       </c>
       <c r="T37">
-        <v>1.546911508004858</v>
+        <v>1.566777666069989</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.736696255505738</v>
+        <v>8.494010248408358</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1474445346150454</v>
+        <v>0.1471029287507183</v>
       </c>
       <c r="C38">
-        <v>1738.973274067226</v>
+        <v>1724.206180078022</v>
       </c>
       <c r="D38">
-        <v>2426.337274067226</v>
+        <v>2434.519180078022</v>
       </c>
       <c r="E38">
-        <v>-792.5360000000001</v>
+        <v>-769.587</v>
       </c>
       <c r="F38">
-        <v>826.164</v>
+        <v>849.1130000000001</v>
       </c>
       <c r="G38">
         <v>138.8</v>
@@ -4391,28 +4391,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M38">
-        <v>44.199774</v>
+        <v>45.4275455</v>
       </c>
       <c r="N38">
-        <v>331.2335593333333</v>
+        <v>330.0057878333333</v>
       </c>
       <c r="O38">
-        <v>82.80838983333334</v>
+        <v>82.50144695833333</v>
       </c>
       <c r="P38">
-        <v>248.4251695</v>
+        <v>247.504340875</v>
       </c>
       <c r="Q38">
-        <v>330.3251695</v>
+        <v>329.404340875</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2078117728360084</v>
+        <v>0.2099312361122513</v>
       </c>
       <c r="T38">
-        <v>1.566777666069989</v>
+        <v>1.587274495819727</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.49401024840836</v>
+        <v>8.264442403856782</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1471029287507183</v>
+        <v>0.1467613228863913</v>
       </c>
       <c r="C39">
-        <v>1724.206180078022</v>
+        <v>1709.494453570042</v>
       </c>
       <c r="D39">
-        <v>2434.519180078022</v>
+        <v>2442.756453570042</v>
       </c>
       <c r="E39">
-        <v>-769.587</v>
+        <v>-746.638</v>
       </c>
       <c r="F39">
-        <v>849.1130000000001</v>
+        <v>872.062</v>
       </c>
       <c r="G39">
         <v>138.8</v>
@@ -4473,28 +4473,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M39">
-        <v>45.4275455</v>
+        <v>46.655317</v>
       </c>
       <c r="N39">
-        <v>330.0057878333333</v>
+        <v>328.7780163333333</v>
       </c>
       <c r="O39">
-        <v>82.50144695833333</v>
+        <v>82.19450408333333</v>
       </c>
       <c r="P39">
-        <v>247.504340875</v>
+        <v>246.58351225</v>
       </c>
       <c r="Q39">
-        <v>329.404340875</v>
+        <v>328.48351225</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2099312361122513</v>
+        <v>0.2121190691715989</v>
       </c>
       <c r="T39">
-        <v>1.587274495819727</v>
+        <v>1.608432513625908</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>8.264442403856782</v>
+        <v>8.046957077439497</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1467613228863913</v>
+        <v>0.1464197170220642</v>
       </c>
       <c r="C40">
-        <v>1709.494453570042</v>
+        <v>1694.838658464261</v>
       </c>
       <c r="D40">
-        <v>2442.756453570042</v>
+        <v>2451.049658464261</v>
       </c>
       <c r="E40">
-        <v>-746.638</v>
+        <v>-723.689</v>
       </c>
       <c r="F40">
-        <v>872.062</v>
+        <v>895.0110000000001</v>
       </c>
       <c r="G40">
         <v>138.8</v>
@@ -4555,28 +4555,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M40">
-        <v>46.655317</v>
+        <v>47.88308850000001</v>
       </c>
       <c r="N40">
-        <v>328.7780163333333</v>
+        <v>327.5502448333334</v>
       </c>
       <c r="O40">
-        <v>82.19450408333333</v>
+        <v>81.88756120833334</v>
       </c>
       <c r="P40">
-        <v>246.58351225</v>
+        <v>245.662683625</v>
       </c>
       <c r="Q40">
-        <v>328.48351225</v>
+        <v>327.562683625</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2121190691715989</v>
+        <v>0.2143786344624004</v>
       </c>
       <c r="T40">
-        <v>1.608432513625908</v>
+        <v>1.630284236933932</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>8.046957077439497</v>
+        <v>7.840624844684639</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1464197170220642</v>
+        <v>0.1460781111577372</v>
       </c>
       <c r="C41">
-        <v>1694.838658464261</v>
+        <v>1680.239366365829</v>
       </c>
       <c r="D41">
-        <v>2451.049658464261</v>
+        <v>2459.399366365829</v>
       </c>
       <c r="E41">
-        <v>-723.689</v>
+        <v>-700.74</v>
       </c>
       <c r="F41">
-        <v>895.0110000000001</v>
+        <v>917.96</v>
       </c>
       <c r="G41">
         <v>138.8</v>
@@ -4637,28 +4637,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M41">
-        <v>47.88308850000001</v>
+        <v>49.11086</v>
       </c>
       <c r="N41">
-        <v>327.5502448333334</v>
+        <v>326.3224733333333</v>
       </c>
       <c r="O41">
-        <v>81.88756120833334</v>
+        <v>81.58061833333333</v>
       </c>
       <c r="P41">
-        <v>245.662683625</v>
+        <v>244.741855</v>
       </c>
       <c r="Q41">
-        <v>327.562683625</v>
+        <v>326.641855</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2143786344624004</v>
+        <v>0.2167135185962287</v>
       </c>
       <c r="T41">
-        <v>1.630284236933932</v>
+        <v>1.652864351018889</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>7.840624844684639</v>
+        <v>7.644609223567523</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1460781111577372</v>
+        <v>0.1459825052934102</v>
       </c>
       <c r="C42">
-        <v>1680.239366365829</v>
+        <v>1659.637412903128</v>
       </c>
       <c r="D42">
-        <v>2459.399366365829</v>
+        <v>2461.746412903128</v>
       </c>
       <c r="E42">
-        <v>-700.74</v>
+        <v>-677.7909999999999</v>
       </c>
       <c r="F42">
-        <v>917.96</v>
+        <v>940.9090000000001</v>
       </c>
       <c r="G42">
         <v>138.8</v>
@@ -4719,45 +4719,45 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M42">
-        <v>49.11086</v>
+        <v>51.09135870000001</v>
       </c>
       <c r="N42">
-        <v>326.3224733333333</v>
+        <v>324.3419746333333</v>
       </c>
       <c r="O42">
-        <v>81.58061833333333</v>
+        <v>81.08549365833333</v>
       </c>
       <c r="P42">
-        <v>244.741855</v>
+        <v>243.256480975</v>
       </c>
       <c r="Q42">
-        <v>326.641855</v>
+        <v>325.156480975</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2167135185962287</v>
+        <v>0.219127551344763</v>
       </c>
       <c r="T42">
-        <v>1.652864351018889</v>
+        <v>1.676209892699947</v>
       </c>
       <c r="U42">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V42">
         <v>0.25</v>
       </c>
       <c r="W42">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y42">
-        <v>7.644609223567523</v>
+        <v>7.348274598407446</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1459825052934102</v>
+        <v>0.1456468994290831</v>
       </c>
       <c r="C43">
-        <v>1659.637412903128</v>
+        <v>1644.962846434669</v>
       </c>
       <c r="D43">
-        <v>2461.746412903128</v>
+        <v>2470.020846434669</v>
       </c>
       <c r="E43">
-        <v>-677.7909999999999</v>
+        <v>-654.8419999999999</v>
       </c>
       <c r="F43">
-        <v>940.9090000000001</v>
+        <v>963.8580000000002</v>
       </c>
       <c r="G43">
         <v>138.8</v>
@@ -4801,28 +4801,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M43">
-        <v>51.09135870000001</v>
+        <v>52.33748940000001</v>
       </c>
       <c r="N43">
-        <v>324.3419746333333</v>
+        <v>323.0958439333333</v>
       </c>
       <c r="O43">
-        <v>81.08549365833333</v>
+        <v>80.77396098333332</v>
       </c>
       <c r="P43">
-        <v>243.256480975</v>
+        <v>242.32188295</v>
       </c>
       <c r="Q43">
-        <v>325.156480975</v>
+        <v>324.22188295</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.219127551344763</v>
+        <v>0.2216248266018674</v>
       </c>
       <c r="T43">
-        <v>1.676209892699947</v>
+        <v>1.700360453059662</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>7.348274598407446</v>
+        <v>7.173315679397744</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1456468994290831</v>
+        <v>0.1453112935647561</v>
       </c>
       <c r="C44">
-        <v>1644.962846434669</v>
+        <v>1630.344091690039</v>
       </c>
       <c r="D44">
-        <v>2470.020846434669</v>
+        <v>2478.351091690039</v>
       </c>
       <c r="E44">
-        <v>-654.8420000000001</v>
+        <v>-631.893</v>
       </c>
       <c r="F44">
-        <v>963.8579999999999</v>
+        <v>986.807</v>
       </c>
       <c r="G44">
         <v>138.8</v>
@@ -4883,28 +4883,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M44">
-        <v>52.3374894</v>
+        <v>53.5836201</v>
       </c>
       <c r="N44">
-        <v>323.0958439333334</v>
+        <v>321.8497132333333</v>
       </c>
       <c r="O44">
-        <v>80.77396098333334</v>
+        <v>80.46242830833333</v>
       </c>
       <c r="P44">
-        <v>242.32188295</v>
+        <v>241.387284925</v>
       </c>
       <c r="Q44">
-        <v>324.22188295</v>
+        <v>323.287284925</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2216248266018674</v>
+        <v>0.2242097255522036</v>
       </c>
       <c r="T44">
-        <v>1.700360453059662</v>
+        <v>1.725358401502173</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>7.173315679397747</v>
+        <v>7.00649438452803</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1453112935647561</v>
+        <v>0.144975687700429</v>
       </c>
       <c r="C45">
-        <v>1630.344091690039</v>
+        <v>1615.781715261986</v>
       </c>
       <c r="D45">
-        <v>2478.351091690039</v>
+        <v>2486.737715261986</v>
       </c>
       <c r="E45">
-        <v>-631.893</v>
+        <v>-608.944</v>
       </c>
       <c r="F45">
-        <v>986.807</v>
+        <v>1009.756</v>
       </c>
       <c r="G45">
         <v>138.8</v>
@@ -4965,28 +4965,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M45">
-        <v>53.5836201</v>
+        <v>54.82975080000001</v>
       </c>
       <c r="N45">
-        <v>321.8497132333333</v>
+        <v>320.6035825333333</v>
       </c>
       <c r="O45">
-        <v>80.46242830833333</v>
+        <v>80.15089563333333</v>
       </c>
       <c r="P45">
-        <v>241.387284925</v>
+        <v>240.4526869</v>
       </c>
       <c r="Q45">
-        <v>323.287284925</v>
+        <v>322.3526869</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2242097255522036</v>
+        <v>0.2268869423221947</v>
       </c>
       <c r="T45">
-        <v>1.725358401502173</v>
+        <v>1.751249133817633</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>7.00649438452803</v>
+        <v>6.847255875788757</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.144975687700429</v>
+        <v>0.144640081836102</v>
       </c>
       <c r="C46">
-        <v>1615.781715261986</v>
+        <v>1601.276291438593</v>
       </c>
       <c r="D46">
-        <v>2486.737715261986</v>
+        <v>2495.181291438593</v>
       </c>
       <c r="E46">
-        <v>-608.944</v>
+        <v>-585.9949999999999</v>
       </c>
       <c r="F46">
-        <v>1009.756</v>
+        <v>1032.705</v>
       </c>
       <c r="G46">
         <v>138.8</v>
@@ -5047,28 +5047,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M46">
-        <v>54.82975080000001</v>
+        <v>56.07588150000001</v>
       </c>
       <c r="N46">
-        <v>320.6035825333333</v>
+        <v>319.3574518333334</v>
       </c>
       <c r="O46">
-        <v>80.15089563333333</v>
+        <v>79.83936295833334</v>
       </c>
       <c r="P46">
-        <v>240.4526869</v>
+        <v>239.518088875</v>
       </c>
       <c r="Q46">
-        <v>322.3526869</v>
+        <v>321.418088875</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2268869423221947</v>
+        <v>0.2296615124292763</v>
       </c>
       <c r="T46">
-        <v>1.751249133817633</v>
+        <v>1.778081347308199</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.847255875788757</v>
+        <v>6.695094634104563</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.144640081836102</v>
+        <v>0.1443044759717749</v>
       </c>
       <c r="C47">
-        <v>1601.276291438593</v>
+        <v>1586.828402334365</v>
       </c>
       <c r="D47">
-        <v>2495.181291438593</v>
+        <v>2503.682402334365</v>
       </c>
       <c r="E47">
-        <v>-585.9949999999999</v>
+        <v>-563.046</v>
       </c>
       <c r="F47">
-        <v>1032.705</v>
+        <v>1055.654</v>
       </c>
       <c r="G47">
         <v>138.8</v>
@@ -5129,28 +5129,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M47">
-        <v>56.07588150000001</v>
+        <v>57.3220122</v>
       </c>
       <c r="N47">
-        <v>319.3574518333334</v>
+        <v>318.1113211333333</v>
       </c>
       <c r="O47">
-        <v>79.83936295833334</v>
+        <v>79.52783028333333</v>
       </c>
       <c r="P47">
-        <v>239.518088875</v>
+        <v>238.58349085</v>
       </c>
       <c r="Q47">
-        <v>321.418088875</v>
+        <v>320.48349085</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2296615124292763</v>
+        <v>0.2325388443921758</v>
       </c>
       <c r="T47">
-        <v>1.778081347308199</v>
+        <v>1.805907346483601</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.695094634104563</v>
+        <v>6.54954909858055</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1443044759717749</v>
+        <v>0.1439688701074479</v>
       </c>
       <c r="C48">
-        <v>1586.828402334365</v>
+        <v>1572.43863802401</v>
       </c>
       <c r="D48">
-        <v>2503.682402334365</v>
+        <v>2512.24163802401</v>
       </c>
       <c r="E48">
-        <v>-563.046</v>
+        <v>-540.097</v>
       </c>
       <c r="F48">
-        <v>1055.654</v>
+        <v>1078.603</v>
       </c>
       <c r="G48">
         <v>138.8</v>
@@ -5211,28 +5211,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M48">
-        <v>57.3220122</v>
+        <v>58.56814290000001</v>
       </c>
       <c r="N48">
-        <v>318.1113211333333</v>
+        <v>316.8651904333333</v>
       </c>
       <c r="O48">
-        <v>79.52783028333333</v>
+        <v>79.21629760833333</v>
       </c>
       <c r="P48">
-        <v>238.58349085</v>
+        <v>237.648892825</v>
       </c>
       <c r="Q48">
-        <v>320.48349085</v>
+        <v>319.548892825</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2325388443921758</v>
+        <v>0.2355247549197129</v>
       </c>
       <c r="T48">
-        <v>1.805907346483601</v>
+        <v>1.834783383363735</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.54954909858055</v>
+        <v>6.410196990100113</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1439688701074479</v>
+        <v>0.1436332642431208</v>
       </c>
       <c r="C49">
-        <v>1572.43863802401</v>
+        <v>1558.107596678974</v>
       </c>
       <c r="D49">
-        <v>2512.24163802401</v>
+        <v>2520.859596678974</v>
       </c>
       <c r="E49">
-        <v>-540.097</v>
+        <v>-517.1479999999999</v>
       </c>
       <c r="F49">
-        <v>1078.603</v>
+        <v>1101.552</v>
       </c>
       <c r="G49">
         <v>138.8</v>
@@ -5293,28 +5293,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M49">
-        <v>58.56814290000001</v>
+        <v>59.81427360000001</v>
       </c>
       <c r="N49">
-        <v>316.8651904333333</v>
+        <v>315.6190597333333</v>
       </c>
       <c r="O49">
-        <v>79.21629760833333</v>
+        <v>78.90476493333333</v>
       </c>
       <c r="P49">
-        <v>237.648892825</v>
+        <v>236.7142948</v>
       </c>
       <c r="Q49">
-        <v>319.548892825</v>
+        <v>318.6142947999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2355247549197129</v>
+        <v>0.2386255081598477</v>
       </c>
       <c r="T49">
-        <v>1.834783383363735</v>
+        <v>1.864770037046952</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>6.410196990100113</v>
+        <v>6.276651219473027</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1436332642431208</v>
+        <v>0.1432976583787938</v>
       </c>
       <c r="C50">
-        <v>1558.107596678975</v>
+        <v>1543.835884706793</v>
       </c>
       <c r="D50">
-        <v>2520.859596678974</v>
+        <v>2529.536884706793</v>
       </c>
       <c r="E50">
-        <v>-517.1480000000001</v>
+        <v>-494.1990000000001</v>
       </c>
       <c r="F50">
-        <v>1101.552</v>
+        <v>1124.501</v>
       </c>
       <c r="G50">
         <v>138.8</v>
@@ -5375,28 +5375,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M50">
-        <v>59.81427359999999</v>
+        <v>61.0604043</v>
       </c>
       <c r="N50">
-        <v>315.6190597333334</v>
+        <v>314.3729290333333</v>
       </c>
       <c r="O50">
-        <v>78.90476493333334</v>
+        <v>78.59323225833333</v>
       </c>
       <c r="P50">
-        <v>236.7142948</v>
+        <v>235.779696775</v>
       </c>
       <c r="Q50">
-        <v>318.6142948</v>
+        <v>317.679696775</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2386255081598477</v>
+        <v>0.2418478595662623</v>
       </c>
       <c r="T50">
-        <v>1.864770037046952</v>
+        <v>1.895932637933431</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>6.276651219473029</v>
+        <v>6.148556296626639</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1432976583787938</v>
+        <v>0.1433370525144667</v>
       </c>
       <c r="C51">
-        <v>1543.835884706793</v>
+        <v>1519.86523276369</v>
       </c>
       <c r="D51">
-        <v>2529.536884706793</v>
+        <v>2528.51523276369</v>
       </c>
       <c r="E51">
-        <v>-494.1990000000001</v>
+        <v>-471.25</v>
       </c>
       <c r="F51">
-        <v>1124.501</v>
+        <v>1147.45</v>
       </c>
       <c r="G51">
         <v>138.8</v>
@@ -5457,45 +5457,45 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M51">
-        <v>61.0604043</v>
+        <v>63.453985</v>
       </c>
       <c r="N51">
-        <v>314.3729290333333</v>
+        <v>311.9793483333333</v>
       </c>
       <c r="O51">
-        <v>78.59323225833333</v>
+        <v>77.99483708333334</v>
       </c>
       <c r="P51">
-        <v>235.779696775</v>
+        <v>233.98451125</v>
       </c>
       <c r="Q51">
-        <v>317.679696775</v>
+        <v>315.88451125</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2418478595662623</v>
+        <v>0.2451991050289335</v>
       </c>
       <c r="T51">
-        <v>1.895932637933431</v>
+        <v>1.928341742855371</v>
       </c>
       <c r="U51">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V51">
         <v>0.25</v>
       </c>
       <c r="W51">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y51">
-        <v>6.148556296626639</v>
+        <v>5.916623413538698</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1433370525144667</v>
+        <v>0.1430089466501397</v>
       </c>
       <c r="C52">
-        <v>1519.86523276369</v>
+        <v>1505.450639364102</v>
       </c>
       <c r="D52">
-        <v>2528.51523276369</v>
+        <v>2537.049639364102</v>
       </c>
       <c r="E52">
-        <v>-471.25</v>
+        <v>-448.3009999999999</v>
       </c>
       <c r="F52">
-        <v>1147.45</v>
+        <v>1170.399</v>
       </c>
       <c r="G52">
         <v>138.8</v>
@@ -5539,28 +5539,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M52">
-        <v>63.453985</v>
+        <v>64.72306470000001</v>
       </c>
       <c r="N52">
-        <v>311.9793483333333</v>
+        <v>310.7102686333333</v>
       </c>
       <c r="O52">
-        <v>77.99483708333334</v>
+        <v>77.67756715833333</v>
       </c>
       <c r="P52">
-        <v>233.98451125</v>
+        <v>233.032701475</v>
       </c>
       <c r="Q52">
-        <v>315.88451125</v>
+        <v>314.932701475</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2451991050289335</v>
+        <v>0.2486871360206932</v>
       </c>
       <c r="T52">
-        <v>1.928341742855371</v>
+        <v>1.962073668386368</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.916623413538698</v>
+        <v>5.800611189743821</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1430089466501397</v>
+        <v>0.1426808407858126</v>
       </c>
       <c r="C53">
-        <v>1505.450639364102</v>
+        <v>1491.093852829761</v>
       </c>
       <c r="D53">
-        <v>2537.049639364102</v>
+        <v>2545.641852829761</v>
       </c>
       <c r="E53">
-        <v>-448.3009999999999</v>
+        <v>-425.3519999999999</v>
       </c>
       <c r="F53">
-        <v>1170.399</v>
+        <v>1193.348</v>
       </c>
       <c r="G53">
         <v>138.8</v>
@@ -5621,28 +5621,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M53">
-        <v>64.72306470000001</v>
+        <v>65.99214440000002</v>
       </c>
       <c r="N53">
-        <v>310.7102686333333</v>
+        <v>309.4411889333333</v>
       </c>
       <c r="O53">
-        <v>77.67756715833333</v>
+        <v>77.36029723333333</v>
       </c>
       <c r="P53">
-        <v>233.032701475</v>
+        <v>232.0808917</v>
       </c>
       <c r="Q53">
-        <v>314.932701475</v>
+        <v>313.9808917</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2486871360206932</v>
+        <v>0.2523205016371096</v>
       </c>
       <c r="T53">
-        <v>1.962073668386368</v>
+        <v>1.997211090814491</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.800611189743821</v>
+        <v>5.689060974556439</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1426808407858126</v>
+        <v>0.1423527349214856</v>
       </c>
       <c r="C54">
-        <v>1491.093852829761</v>
+        <v>1476.795462479182</v>
       </c>
       <c r="D54">
-        <v>2545.641852829761</v>
+        <v>2554.292462479182</v>
       </c>
       <c r="E54">
-        <v>-425.3519999999999</v>
+        <v>-402.403</v>
       </c>
       <c r="F54">
-        <v>1193.348</v>
+        <v>1216.297</v>
       </c>
       <c r="G54">
         <v>138.8</v>
@@ -5703,28 +5703,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M54">
-        <v>65.99214440000002</v>
+        <v>67.26122410000001</v>
       </c>
       <c r="N54">
-        <v>309.4411889333333</v>
+        <v>308.1721092333333</v>
       </c>
       <c r="O54">
-        <v>77.36029723333333</v>
+        <v>77.04302730833334</v>
       </c>
       <c r="P54">
-        <v>232.0808917</v>
+        <v>231.129081925</v>
       </c>
       <c r="Q54">
-        <v>313.9808917</v>
+        <v>313.029081925</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2523205016371096</v>
+        <v>0.2561084785563523</v>
       </c>
       <c r="T54">
-        <v>1.997211090814491</v>
+        <v>2.03384372270764</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.689060974556439</v>
+        <v>5.581720201451602</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1423527349214856</v>
+        <v>0.1420246290571585</v>
       </c>
       <c r="C55">
-        <v>1476.795462479182</v>
+        <v>1462.556065668694</v>
       </c>
       <c r="D55">
-        <v>2554.292462479182</v>
+        <v>2563.002065668694</v>
       </c>
       <c r="E55">
-        <v>-402.403</v>
+        <v>-379.454</v>
       </c>
       <c r="F55">
-        <v>1216.297</v>
+        <v>1239.246</v>
       </c>
       <c r="G55">
         <v>138.8</v>
@@ -5785,28 +5785,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M55">
-        <v>67.26122410000001</v>
+        <v>68.53030380000001</v>
       </c>
       <c r="N55">
-        <v>308.1721092333333</v>
+        <v>306.9030295333333</v>
       </c>
       <c r="O55">
-        <v>77.04302730833334</v>
+        <v>76.72575738333333</v>
       </c>
       <c r="P55">
-        <v>231.129081925</v>
+        <v>230.17727215</v>
       </c>
       <c r="Q55">
-        <v>313.029081925</v>
+        <v>312.07727215</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2561084785563523</v>
+        <v>0.2600611501242577</v>
       </c>
       <c r="T55">
-        <v>2.03384372270764</v>
+        <v>2.072069077726578</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.581720201451602</v>
+        <v>5.478355012535831</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1420246290571585</v>
+        <v>0.1416965231928315</v>
       </c>
       <c r="C56">
-        <v>1462.556065668694</v>
+        <v>1448.37626792994</v>
       </c>
       <c r="D56">
-        <v>2563.002065668694</v>
+        <v>2571.77126792994</v>
       </c>
       <c r="E56">
-        <v>-379.454</v>
+        <v>-356.5049999999999</v>
       </c>
       <c r="F56">
-        <v>1239.246</v>
+        <v>1262.195</v>
       </c>
       <c r="G56">
         <v>138.8</v>
@@ -5867,28 +5867,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M56">
-        <v>68.53030380000001</v>
+        <v>69.7993835</v>
       </c>
       <c r="N56">
-        <v>306.9030295333333</v>
+        <v>305.6339498333333</v>
       </c>
       <c r="O56">
-        <v>76.72575738333333</v>
+        <v>76.40848745833333</v>
       </c>
       <c r="P56">
-        <v>230.17727215</v>
+        <v>229.225462375</v>
       </c>
       <c r="Q56">
-        <v>312.07727215</v>
+        <v>311.125462375</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2600611501242577</v>
+        <v>0.26418949598407</v>
       </c>
       <c r="T56">
-        <v>2.072069077726578</v>
+        <v>2.111993337413025</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.478355012535831</v>
+        <v>5.378748557762452</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1416965231928315</v>
+        <v>0.1413684173285044</v>
       </c>
       <c r="C57">
-        <v>1448.37626792994</v>
+        <v>1434.25668311022</v>
       </c>
       <c r="D57">
-        <v>2571.77126792994</v>
+        <v>2580.60068311022</v>
       </c>
       <c r="E57">
-        <v>-356.5049999999999</v>
+        <v>-333.5559999999998</v>
       </c>
       <c r="F57">
-        <v>1262.195</v>
+        <v>1285.144</v>
       </c>
       <c r="G57">
         <v>138.8</v>
@@ -5949,28 +5949,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M57">
-        <v>69.7993835</v>
+        <v>71.06846320000001</v>
       </c>
       <c r="N57">
-        <v>305.6339498333333</v>
+        <v>304.3648701333333</v>
       </c>
       <c r="O57">
-        <v>76.40848745833333</v>
+        <v>76.09121753333334</v>
       </c>
       <c r="P57">
-        <v>229.225462375</v>
+        <v>228.2736526</v>
       </c>
       <c r="Q57">
-        <v>311.125462375</v>
+        <v>310.1736526</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.26418949598407</v>
+        <v>0.2685054939284192</v>
       </c>
       <c r="T57">
-        <v>2.111993337413025</v>
+        <v>2.153732336176128</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.378748557762452</v>
+        <v>5.282699476373837</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1413684173285044</v>
+        <v>0.1410403114641774</v>
       </c>
       <c r="C58">
-        <v>1434.25668311022</v>
+        <v>1420.197933515725</v>
       </c>
       <c r="D58">
-        <v>2580.60068311022</v>
+        <v>2589.490933515725</v>
       </c>
       <c r="E58">
-        <v>-333.5559999999998</v>
+        <v>-310.6069999999997</v>
       </c>
       <c r="F58">
-        <v>1285.144</v>
+        <v>1308.093</v>
       </c>
       <c r="G58">
         <v>138.8</v>
@@ -6031,28 +6031,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M58">
-        <v>71.06846320000001</v>
+        <v>72.33754290000002</v>
       </c>
       <c r="N58">
-        <v>304.3648701333333</v>
+        <v>303.0957904333333</v>
       </c>
       <c r="O58">
-        <v>76.09121753333334</v>
+        <v>75.77394760833333</v>
       </c>
       <c r="P58">
-        <v>228.2736526</v>
+        <v>227.321842825</v>
       </c>
       <c r="Q58">
-        <v>310.1736526</v>
+        <v>309.221842825</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2685054939284192</v>
+        <v>0.2730222359632032</v>
       </c>
       <c r="T58">
-        <v>2.153732336176128</v>
+        <v>2.197412683718911</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.282699476373837</v>
+        <v>5.190020538191839</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1410403114641774</v>
+        <v>0.1407122055998503</v>
       </c>
       <c r="C59">
-        <v>1420.197933515725</v>
+        <v>1406.20065005775</v>
       </c>
       <c r="D59">
-        <v>2589.490933515725</v>
+        <v>2598.44265005775</v>
       </c>
       <c r="E59">
-        <v>-310.6069999999997</v>
+        <v>-287.6579999999999</v>
       </c>
       <c r="F59">
-        <v>1308.093</v>
+        <v>1331.042</v>
       </c>
       <c r="G59">
         <v>138.8</v>
@@ -6113,28 +6113,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M59">
-        <v>72.33754290000002</v>
+        <v>73.60662260000001</v>
       </c>
       <c r="N59">
-        <v>303.0957904333333</v>
+        <v>301.8267107333334</v>
       </c>
       <c r="O59">
-        <v>75.77394760833333</v>
+        <v>75.45667768333334</v>
       </c>
       <c r="P59">
-        <v>227.321842825</v>
+        <v>226.37003305</v>
       </c>
       <c r="Q59">
-        <v>309.221842825</v>
+        <v>308.27003305</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2730222359632032</v>
+        <v>0.2777540609520247</v>
       </c>
       <c r="T59">
-        <v>2.197412683718911</v>
+        <v>2.24317304781135</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.190020538191839</v>
+        <v>5.100537425464394</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1407122055998503</v>
+        <v>0.1403840997355233</v>
       </c>
       <c r="C60">
-        <v>1406.20065005775</v>
+        <v>1392.265472401943</v>
       </c>
       <c r="D60">
-        <v>2598.44265005775</v>
+        <v>2607.456472401943</v>
       </c>
       <c r="E60">
-        <v>-287.6580000000001</v>
+        <v>-264.7090000000001</v>
       </c>
       <c r="F60">
-        <v>1331.042</v>
+        <v>1353.991</v>
       </c>
       <c r="G60">
         <v>138.8</v>
@@ -6195,28 +6195,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M60">
-        <v>73.60662259999999</v>
+        <v>74.8757023</v>
       </c>
       <c r="N60">
-        <v>301.8267107333334</v>
+        <v>300.5576310333333</v>
       </c>
       <c r="O60">
-        <v>75.45667768333334</v>
+        <v>75.13940775833333</v>
       </c>
       <c r="P60">
-        <v>226.37003305</v>
+        <v>225.418223275</v>
       </c>
       <c r="Q60">
-        <v>308.27003305</v>
+        <v>307.318223275</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2777540609520246</v>
+        <v>0.282716706672008</v>
       </c>
       <c r="T60">
-        <v>2.243173047811349</v>
+        <v>2.291165624786346</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.100537425464395</v>
+        <v>5.014087638592117</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1403840997355233</v>
+        <v>0.1400559938711962</v>
       </c>
       <c r="C61">
-        <v>1392.265472401943</v>
+        <v>1378.393049120679</v>
       </c>
       <c r="D61">
-        <v>2607.456472401943</v>
+        <v>2616.533049120679</v>
       </c>
       <c r="E61">
-        <v>-264.7090000000001</v>
+        <v>-241.76</v>
       </c>
       <c r="F61">
-        <v>1353.991</v>
+        <v>1376.94</v>
       </c>
       <c r="G61">
         <v>138.8</v>
@@ -6277,28 +6277,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M61">
-        <v>74.8757023</v>
+        <v>76.14478200000001</v>
       </c>
       <c r="N61">
-        <v>300.5576310333333</v>
+        <v>299.2885513333333</v>
       </c>
       <c r="O61">
-        <v>75.13940775833333</v>
+        <v>74.82213783333333</v>
       </c>
       <c r="P61">
-        <v>225.418223275</v>
+        <v>224.4664135</v>
       </c>
       <c r="Q61">
-        <v>307.318223275</v>
+        <v>306.3664135</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.282716706672008</v>
+        <v>0.2879274846779906</v>
       </c>
       <c r="T61">
-        <v>2.291165624786346</v>
+        <v>2.341557830610093</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.014087638592117</v>
+        <v>4.930519511282247</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1400559938711962</v>
+        <v>0.1397278880068692</v>
       </c>
       <c r="C62">
-        <v>1378.393049120679</v>
+        <v>1364.584037848619</v>
       </c>
       <c r="D62">
-        <v>2616.533049120679</v>
+        <v>2625.673037848619</v>
       </c>
       <c r="E62">
-        <v>-241.76</v>
+        <v>-218.8109999999999</v>
       </c>
       <c r="F62">
-        <v>1376.94</v>
+        <v>1399.889</v>
       </c>
       <c r="G62">
         <v>138.8</v>
@@ -6359,28 +6359,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M62">
-        <v>76.14478200000001</v>
+        <v>77.41386170000001</v>
       </c>
       <c r="N62">
-        <v>299.2885513333333</v>
+        <v>298.0194716333333</v>
       </c>
       <c r="O62">
-        <v>74.82213783333333</v>
+        <v>74.50486790833332</v>
       </c>
       <c r="P62">
-        <v>224.4664135</v>
+        <v>223.514603725</v>
       </c>
       <c r="Q62">
-        <v>306.3664135</v>
+        <v>305.4146037249999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2879274846779906</v>
+        <v>0.2934054820688954</v>
       </c>
       <c r="T62">
-        <v>2.341557830610093</v>
+        <v>2.394534252117109</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.930519511282247</v>
+        <v>4.849691322572703</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1397278880068692</v>
+        <v>0.1393997821425422</v>
       </c>
       <c r="C63">
-        <v>1364.584037848619</v>
+        <v>1350.839105441549</v>
       </c>
       <c r="D63">
-        <v>2625.673037848619</v>
+        <v>2634.877105441549</v>
       </c>
       <c r="E63">
-        <v>-218.8109999999999</v>
+        <v>-195.8620000000001</v>
       </c>
       <c r="F63">
-        <v>1399.889</v>
+        <v>1422.838</v>
       </c>
       <c r="G63">
         <v>138.8</v>
@@ -6441,28 +6441,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M63">
-        <v>77.41386170000001</v>
+        <v>78.6829414</v>
       </c>
       <c r="N63">
-        <v>298.0194716333333</v>
+        <v>296.7503919333333</v>
       </c>
       <c r="O63">
-        <v>74.50486790833332</v>
+        <v>74.18759798333333</v>
       </c>
       <c r="P63">
-        <v>223.514603725</v>
+        <v>222.56279395</v>
       </c>
       <c r="Q63">
-        <v>305.4146037249999</v>
+        <v>304.46279395</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2934054820688954</v>
+        <v>0.2991717951119531</v>
       </c>
       <c r="T63">
-        <v>2.394534252117109</v>
+        <v>2.45029890633502</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.849691322572703</v>
+        <v>4.771470494789272</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1393997821425422</v>
+        <v>0.1390716762782151</v>
       </c>
       <c r="C64">
-        <v>1350.839105441549</v>
+        <v>1337.158928138568</v>
       </c>
       <c r="D64">
-        <v>2634.877105441549</v>
+        <v>2644.145928138568</v>
       </c>
       <c r="E64">
-        <v>-195.8620000000001</v>
+        <v>-172.913</v>
       </c>
       <c r="F64">
-        <v>1422.838</v>
+        <v>1445.787</v>
       </c>
       <c r="G64">
         <v>138.8</v>
@@ -6523,28 +6523,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M64">
-        <v>78.6829414</v>
+        <v>79.95202110000001</v>
       </c>
       <c r="N64">
-        <v>296.7503919333333</v>
+        <v>295.4813122333333</v>
       </c>
       <c r="O64">
-        <v>74.18759798333333</v>
+        <v>73.87032805833333</v>
       </c>
       <c r="P64">
-        <v>222.56279395</v>
+        <v>221.610984175</v>
       </c>
       <c r="Q64">
-        <v>304.46279395</v>
+        <v>303.510984175</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2991717951119531</v>
+        <v>0.3052498007519328</v>
       </c>
       <c r="T64">
-        <v>2.45029890633502</v>
+        <v>2.509077866186332</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.771470494789272</v>
+        <v>4.695732867887855</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1390716762782151</v>
+        <v>0.1387435704138881</v>
       </c>
       <c r="C65">
-        <v>1337.158928138568</v>
+        <v>1323.544191727705</v>
       </c>
       <c r="D65">
-        <v>2644.145928138568</v>
+        <v>2653.480191727705</v>
       </c>
       <c r="E65">
-        <v>-172.913</v>
+        <v>-149.9639999999999</v>
       </c>
       <c r="F65">
-        <v>1445.787</v>
+        <v>1468.736</v>
       </c>
       <c r="G65">
         <v>138.8</v>
@@ -6605,28 +6605,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M65">
-        <v>79.95202110000001</v>
+        <v>81.2211008</v>
       </c>
       <c r="N65">
-        <v>295.4813122333333</v>
+        <v>294.2122325333333</v>
       </c>
       <c r="O65">
-        <v>73.87032805833333</v>
+        <v>73.55305813333334</v>
       </c>
       <c r="P65">
-        <v>221.610984175</v>
+        <v>220.6591744</v>
       </c>
       <c r="Q65">
-        <v>303.510984175</v>
+        <v>302.5591744</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3052498007519328</v>
+        <v>0.3116654733719113</v>
       </c>
       <c r="T65">
-        <v>2.509077866186332</v>
+        <v>2.571122323807161</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.695732867887855</v>
+        <v>4.622362041827108</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1387435704138881</v>
+        <v>0.138415464549561</v>
       </c>
       <c r="C66">
-        <v>1323.544191727705</v>
+        <v>1309.99559171507</v>
       </c>
       <c r="D66">
-        <v>2653.480191727705</v>
+        <v>2662.88059171507</v>
       </c>
       <c r="E66">
-        <v>-149.9639999999999</v>
+        <v>-127.0149999999999</v>
       </c>
       <c r="F66">
-        <v>1468.736</v>
+        <v>1491.685</v>
       </c>
       <c r="G66">
         <v>138.8</v>
@@ -6687,28 +6687,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M66">
-        <v>81.2211008</v>
+        <v>82.49018050000001</v>
       </c>
       <c r="N66">
-        <v>294.2122325333333</v>
+        <v>292.9431528333333</v>
       </c>
       <c r="O66">
-        <v>73.55305813333334</v>
+        <v>73.23578820833333</v>
       </c>
       <c r="P66">
-        <v>220.6591744</v>
+        <v>219.707364625</v>
       </c>
       <c r="Q66">
-        <v>302.5591744</v>
+        <v>301.6073646249999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3116654733719113</v>
+        <v>0.3184477558558886</v>
       </c>
       <c r="T66">
-        <v>2.571122323807161</v>
+        <v>2.636712179006323</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.622362041827108</v>
+        <v>4.551248779645151</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.138415464549561</v>
+        <v>0.1393248586852339</v>
       </c>
       <c r="C67">
-        <v>1309.99559171507</v>
+        <v>1261.153925015053</v>
       </c>
       <c r="D67">
-        <v>2662.88059171507</v>
+        <v>2636.987925015053</v>
       </c>
       <c r="E67">
-        <v>-127.0149999999999</v>
+        <v>-104.0659999999998</v>
       </c>
       <c r="F67">
-        <v>1491.685</v>
+        <v>1514.634</v>
       </c>
       <c r="G67">
         <v>138.8</v>
@@ -6769,45 +6769,45 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M67">
-        <v>82.49018050000001</v>
+        <v>87.54584520000002</v>
       </c>
       <c r="N67">
-        <v>292.9431528333333</v>
+        <v>287.8874881333333</v>
       </c>
       <c r="O67">
-        <v>73.23578820833333</v>
+        <v>71.97187203333333</v>
       </c>
       <c r="P67">
-        <v>219.707364625</v>
+        <v>215.9156161</v>
       </c>
       <c r="Q67">
-        <v>301.6073646249999</v>
+        <v>297.8156160999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3184477558558886</v>
+        <v>0.3256289961330411</v>
       </c>
       <c r="T67">
-        <v>2.636712179006323</v>
+        <v>2.706160260981907</v>
       </c>
       <c r="U67">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V67">
         <v>0.25</v>
       </c>
       <c r="W67">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y67">
-        <v>4.551248779645151</v>
+        <v>4.288419769957664</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1393248586852339</v>
+        <v>0.1390155028209069</v>
       </c>
       <c r="C68">
-        <v>1261.153925015053</v>
+        <v>1246.956341400483</v>
       </c>
       <c r="D68">
-        <v>2636.987925015053</v>
+        <v>2645.739341400483</v>
       </c>
       <c r="E68">
-        <v>-104.0659999999998</v>
+        <v>-81.11699999999996</v>
       </c>
       <c r="F68">
-        <v>1514.634</v>
+        <v>1537.583</v>
       </c>
       <c r="G68">
         <v>138.8</v>
@@ -6851,28 +6851,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M68">
-        <v>87.54584520000002</v>
+        <v>88.87229740000001</v>
       </c>
       <c r="N68">
-        <v>287.8874881333333</v>
+        <v>286.5610359333333</v>
       </c>
       <c r="O68">
-        <v>71.97187203333333</v>
+        <v>71.64025898333333</v>
       </c>
       <c r="P68">
-        <v>215.9156161</v>
+        <v>214.92077695</v>
       </c>
       <c r="Q68">
-        <v>297.8156160999999</v>
+        <v>296.82077695</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3256289961330411</v>
+        <v>0.3332454630936574</v>
       </c>
       <c r="T68">
-        <v>2.706160260981907</v>
+        <v>2.779817317622677</v>
       </c>
       <c r="U68">
         <v>0.0578</v>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.288419769957664</v>
+        <v>4.224413504734415</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1390155028209069</v>
+        <v>0.1387061469565799</v>
       </c>
       <c r="C69">
-        <v>1246.956341400483</v>
+        <v>1232.81703814881</v>
       </c>
       <c r="D69">
-        <v>2645.739341400483</v>
+        <v>2654.54903814881</v>
       </c>
       <c r="E69">
-        <v>-81.11699999999996</v>
+        <v>-58.16799999999989</v>
       </c>
       <c r="F69">
-        <v>1537.583</v>
+        <v>1560.532</v>
       </c>
       <c r="G69">
         <v>138.8</v>
@@ -6933,28 +6933,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M69">
-        <v>88.87229740000001</v>
+        <v>90.19874960000001</v>
       </c>
       <c r="N69">
-        <v>286.5610359333333</v>
+        <v>285.2345837333334</v>
       </c>
       <c r="O69">
-        <v>71.64025898333333</v>
+        <v>71.30864593333334</v>
       </c>
       <c r="P69">
-        <v>214.92077695</v>
+        <v>213.9259378</v>
       </c>
       <c r="Q69">
-        <v>296.82077695</v>
+        <v>295.8259378</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3332454630936574</v>
+        <v>0.3413379592393121</v>
       </c>
       <c r="T69">
-        <v>2.779817317622677</v>
+        <v>2.858077940303496</v>
       </c>
       <c r="U69">
         <v>0.0578</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.224413504734415</v>
+        <v>4.162289776723616</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1387061469565799</v>
+        <v>0.1383967910922528</v>
       </c>
       <c r="C70">
-        <v>1232.81703814881</v>
+        <v>1218.736599385203</v>
       </c>
       <c r="D70">
-        <v>2654.54903814881</v>
+        <v>2663.417599385203</v>
       </c>
       <c r="E70">
-        <v>-58.16799999999989</v>
+        <v>-35.21899999999982</v>
       </c>
       <c r="F70">
-        <v>1560.532</v>
+        <v>1583.481</v>
       </c>
       <c r="G70">
         <v>138.8</v>
@@ -7015,28 +7015,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M70">
-        <v>90.19874960000001</v>
+        <v>91.52520180000002</v>
       </c>
       <c r="N70">
-        <v>285.2345837333334</v>
+        <v>283.9081315333333</v>
       </c>
       <c r="O70">
-        <v>71.30864593333334</v>
+        <v>70.97703288333332</v>
       </c>
       <c r="P70">
-        <v>213.9259378</v>
+        <v>212.93109865</v>
       </c>
       <c r="Q70">
-        <v>295.8259378</v>
+        <v>294.8310986499999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3413379592393121</v>
+        <v>0.349952551910493</v>
       </c>
       <c r="T70">
-        <v>2.858077940303496</v>
+        <v>2.941387635415335</v>
       </c>
       <c r="U70">
         <v>0.0578</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.162289776723616</v>
+        <v>4.101966736481243</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1383967910922528</v>
+        <v>0.1380874352279258</v>
       </c>
       <c r="C71">
-        <v>1218.736599385203</v>
+        <v>1204.71561706699</v>
       </c>
       <c r="D71">
-        <v>2663.417599385203</v>
+        <v>2672.34561706699</v>
       </c>
       <c r="E71">
-        <v>-35.21899999999982</v>
+        <v>-12.26999999999975</v>
       </c>
       <c r="F71">
-        <v>1583.481</v>
+        <v>1606.43</v>
       </c>
       <c r="G71">
         <v>138.8</v>
@@ -7097,28 +7097,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M71">
-        <v>91.52520180000002</v>
+        <v>92.85165400000002</v>
       </c>
       <c r="N71">
-        <v>283.9081315333333</v>
+        <v>282.5816793333333</v>
       </c>
       <c r="O71">
-        <v>70.97703288333332</v>
+        <v>70.64541983333334</v>
       </c>
       <c r="P71">
-        <v>212.93109865</v>
+        <v>211.9362595</v>
       </c>
       <c r="Q71">
-        <v>294.8310986499999</v>
+        <v>293.8362595</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.349952551910493</v>
+        <v>0.3591414507597526</v>
       </c>
       <c r="T71">
-        <v>2.941387635415335</v>
+        <v>3.030251310201297</v>
       </c>
       <c r="U71">
         <v>0.0578</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.101966736481243</v>
+        <v>4.043367211674369</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1380874352279258</v>
+        <v>0.1396418293635987</v>
       </c>
       <c r="C72">
-        <v>1204.71561706699</v>
+        <v>1137.501939110151</v>
       </c>
       <c r="D72">
-        <v>2672.34561706699</v>
+        <v>2628.080939110151</v>
       </c>
       <c r="E72">
-        <v>-12.26999999999975</v>
+        <v>10.67900000000009</v>
       </c>
       <c r="F72">
-        <v>1606.43</v>
+        <v>1629.379</v>
       </c>
       <c r="G72">
         <v>138.8</v>
@@ -7179,45 +7179,45 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M72">
-        <v>92.85165400000002</v>
+        <v>99.8809327</v>
       </c>
       <c r="N72">
-        <v>282.5816793333333</v>
+        <v>275.5524006333333</v>
       </c>
       <c r="O72">
-        <v>70.64541983333334</v>
+        <v>68.88810015833333</v>
       </c>
       <c r="P72">
-        <v>211.9362595</v>
+        <v>206.664300475</v>
       </c>
       <c r="Q72">
-        <v>293.8362595</v>
+        <v>288.564300475</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3591414507597526</v>
+        <v>0.3689640667710302</v>
       </c>
       <c r="T72">
-        <v>3.030251310201297</v>
+        <v>3.125243514282843</v>
       </c>
       <c r="U72">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V72">
         <v>0.25</v>
       </c>
       <c r="W72">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y72">
-        <v>4.043367211674369</v>
+        <v>3.758808845537876</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1396418293635987</v>
+        <v>0.1393587234992717</v>
       </c>
       <c r="C73">
-        <v>1137.501939110151</v>
+        <v>1122.505432452945</v>
       </c>
       <c r="D73">
-        <v>2628.080939110151</v>
+        <v>2636.033432452945</v>
       </c>
       <c r="E73">
-        <v>10.67899999999986</v>
+        <v>33.62799999999993</v>
       </c>
       <c r="F73">
-        <v>1629.379</v>
+        <v>1652.328</v>
       </c>
       <c r="G73">
         <v>138.8</v>
@@ -7261,28 +7261,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M73">
-        <v>99.88093269999999</v>
+        <v>101.2877064</v>
       </c>
       <c r="N73">
-        <v>275.5524006333334</v>
+        <v>274.1456269333333</v>
       </c>
       <c r="O73">
-        <v>68.88810015833334</v>
+        <v>68.53640673333334</v>
       </c>
       <c r="P73">
-        <v>206.664300475</v>
+        <v>205.6092202</v>
       </c>
       <c r="Q73">
-        <v>288.564300475</v>
+        <v>287.5092202</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3689640667710301</v>
+        <v>0.3794882982116846</v>
       </c>
       <c r="T73">
-        <v>3.125243514282842</v>
+        <v>3.227020875798783</v>
       </c>
       <c r="U73">
         <v>0.0613</v>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.758808845537877</v>
+        <v>3.706603167127628</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1393587234992717</v>
+        <v>0.1390756176349446</v>
       </c>
       <c r="C74">
-        <v>1122.505432452945</v>
+        <v>1107.557199879759</v>
       </c>
       <c r="D74">
-        <v>2636.033432452945</v>
+        <v>2644.034199879758</v>
       </c>
       <c r="E74">
-        <v>33.62799999999993</v>
+        <v>56.577</v>
       </c>
       <c r="F74">
-        <v>1652.328</v>
+        <v>1675.277</v>
       </c>
       <c r="G74">
         <v>138.8</v>
@@ -7343,28 +7343,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M74">
-        <v>101.2877064</v>
+        <v>102.6944801</v>
       </c>
       <c r="N74">
-        <v>274.1456269333333</v>
+        <v>272.7388532333333</v>
       </c>
       <c r="O74">
-        <v>68.53640673333334</v>
+        <v>68.18471330833333</v>
       </c>
       <c r="P74">
-        <v>205.6092202</v>
+        <v>204.554139925</v>
       </c>
       <c r="Q74">
-        <v>287.5092202</v>
+        <v>286.4541399249999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3794882982116846</v>
+        <v>0.3907921023516467</v>
       </c>
       <c r="T74">
-        <v>3.227020875798783</v>
+        <v>3.33633730113072</v>
       </c>
       <c r="U74">
         <v>0.0613</v>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.706603167127628</v>
+        <v>3.655827781276564</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1390756176349446</v>
+        <v>0.1387925117706176</v>
       </c>
       <c r="C75">
-        <v>1107.557199879759</v>
+        <v>1092.657682286618</v>
       </c>
       <c r="D75">
-        <v>2644.034199879758</v>
+        <v>2652.083682286618</v>
       </c>
       <c r="E75">
-        <v>56.577</v>
+        <v>79.52600000000007</v>
       </c>
       <c r="F75">
-        <v>1675.277</v>
+        <v>1698.226</v>
       </c>
       <c r="G75">
         <v>138.8</v>
@@ -7425,28 +7425,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M75">
-        <v>102.6944801</v>
+        <v>104.1012538</v>
       </c>
       <c r="N75">
-        <v>272.7388532333333</v>
+        <v>271.3320795333333</v>
       </c>
       <c r="O75">
-        <v>68.18471330833333</v>
+        <v>67.83301988333334</v>
       </c>
       <c r="P75">
-        <v>204.554139925</v>
+        <v>203.49905965</v>
       </c>
       <c r="Q75">
-        <v>286.4541399249999</v>
+        <v>285.39905965</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3907921023516467</v>
+        <v>0.4029654298869906</v>
       </c>
       <c r="T75">
-        <v>3.33633730113072</v>
+        <v>3.454062682257422</v>
       </c>
       <c r="U75">
         <v>0.0613</v>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.655827781276564</v>
+        <v>3.606424703151206</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1387925117706176</v>
+        <v>0.1385094059062905</v>
       </c>
       <c r="C76">
-        <v>1092.657682286618</v>
+        <v>1077.807325954988</v>
       </c>
       <c r="D76">
-        <v>2652.083682286618</v>
+        <v>2660.182325954988</v>
       </c>
       <c r="E76">
-        <v>79.52600000000007</v>
+        <v>102.4750000000001</v>
       </c>
       <c r="F76">
-        <v>1698.226</v>
+        <v>1721.175</v>
       </c>
       <c r="G76">
         <v>138.8</v>
@@ -7507,28 +7507,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M76">
-        <v>104.1012538</v>
+        <v>105.5080275</v>
       </c>
       <c r="N76">
-        <v>271.3320795333333</v>
+        <v>269.9253058333333</v>
       </c>
       <c r="O76">
-        <v>67.83301988333334</v>
+        <v>67.48132645833333</v>
       </c>
       <c r="P76">
-        <v>203.49905965</v>
+        <v>202.443979375</v>
       </c>
       <c r="Q76">
-        <v>285.39905965</v>
+        <v>284.3439793749999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4029654298869906</v>
+        <v>0.4161126236251622</v>
       </c>
       <c r="T76">
-        <v>3.454062682257422</v>
+        <v>3.58120609387426</v>
       </c>
       <c r="U76">
         <v>0.0613</v>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.606424703151206</v>
+        <v>3.558339040442522</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1385094059062905</v>
+        <v>0.1382263000419635</v>
       </c>
       <c r="C77">
-        <v>1077.807325954988</v>
+        <v>1063.006582634258</v>
       </c>
       <c r="D77">
-        <v>2660.182325954988</v>
+        <v>2668.330582634258</v>
       </c>
       <c r="E77">
-        <v>102.4750000000001</v>
+        <v>125.424</v>
       </c>
       <c r="F77">
-        <v>1721.175</v>
+        <v>1744.124</v>
       </c>
       <c r="G77">
         <v>138.8</v>
@@ -7589,28 +7589,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M77">
-        <v>105.5080275</v>
+        <v>106.9148012</v>
       </c>
       <c r="N77">
-        <v>269.9253058333333</v>
+        <v>268.5185321333333</v>
       </c>
       <c r="O77">
-        <v>67.48132645833333</v>
+        <v>67.12963303333333</v>
       </c>
       <c r="P77">
-        <v>202.443979375</v>
+        <v>201.3888991</v>
       </c>
       <c r="Q77">
-        <v>284.3439793749999</v>
+        <v>283.2888991</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4161126236251622</v>
+        <v>0.4303554168415145</v>
       </c>
       <c r="T77">
-        <v>3.58120609387426</v>
+        <v>3.7189447897925</v>
       </c>
       <c r="U77">
         <v>0.0613</v>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.558339040442522</v>
+        <v>3.511518789910385</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1382263000419635</v>
+        <v>0.1395601941776365</v>
       </c>
       <c r="C78">
-        <v>1063.006582634258</v>
+        <v>1002.096158306687</v>
       </c>
       <c r="D78">
-        <v>2668.330582634258</v>
+        <v>2630.369158306687</v>
       </c>
       <c r="E78">
-        <v>125.424</v>
+        <v>148.373</v>
       </c>
       <c r="F78">
-        <v>1744.124</v>
+        <v>1767.073</v>
       </c>
       <c r="G78">
         <v>138.8</v>
@@ -7671,45 +7671,45 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M78">
-        <v>106.9148012</v>
+        <v>113.2693793</v>
       </c>
       <c r="N78">
-        <v>268.5185321333333</v>
+        <v>262.1639540333333</v>
       </c>
       <c r="O78">
-        <v>67.12963303333333</v>
+        <v>65.54098850833333</v>
       </c>
       <c r="P78">
-        <v>201.3888991</v>
+        <v>196.622965525</v>
       </c>
       <c r="Q78">
-        <v>283.2888991</v>
+        <v>278.522965525</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4303554168415145</v>
+        <v>0.4458367138158106</v>
       </c>
       <c r="T78">
-        <v>3.7189447897925</v>
+        <v>3.868660763616675</v>
       </c>
       <c r="U78">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V78">
         <v>0.25</v>
       </c>
       <c r="W78">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y78">
-        <v>3.511518789910385</v>
+        <v>3.314517441990902</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1395601941776365</v>
+        <v>0.1392980883133094</v>
       </c>
       <c r="C79">
-        <v>1002.096158306687</v>
+        <v>986.5209473774005</v>
       </c>
       <c r="D79">
-        <v>2630.369158306687</v>
+        <v>2637.7429473774</v>
       </c>
       <c r="E79">
-        <v>148.373</v>
+        <v>171.3220000000001</v>
       </c>
       <c r="F79">
-        <v>1767.073</v>
+        <v>1790.022</v>
       </c>
       <c r="G79">
         <v>138.8</v>
@@ -7753,28 +7753,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M79">
-        <v>113.2693793</v>
+        <v>114.7404102</v>
       </c>
       <c r="N79">
-        <v>262.1639540333333</v>
+        <v>260.6929231333334</v>
       </c>
       <c r="O79">
-        <v>65.54098850833333</v>
+        <v>65.17323078333334</v>
       </c>
       <c r="P79">
-        <v>196.622965525</v>
+        <v>195.51969235</v>
       </c>
       <c r="Q79">
-        <v>278.522965525</v>
+        <v>277.41969235</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4458367138158106</v>
+        <v>0.4627254014241336</v>
       </c>
       <c r="T79">
-        <v>3.868660763616675</v>
+        <v>4.031987280515775</v>
       </c>
       <c r="U79">
         <v>0.0641</v>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.314517441990902</v>
+        <v>3.272023628632045</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1392980883133094</v>
+        <v>0.1390359824489824</v>
       </c>
       <c r="C80">
-        <v>986.5209473774005</v>
+        <v>970.987194977469</v>
       </c>
       <c r="D80">
-        <v>2637.7429473774</v>
+        <v>2645.158194977469</v>
       </c>
       <c r="E80">
-        <v>171.3220000000001</v>
+        <v>194.2710000000002</v>
       </c>
       <c r="F80">
-        <v>1790.022</v>
+        <v>1812.971</v>
       </c>
       <c r="G80">
         <v>138.8</v>
@@ -7835,28 +7835,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M80">
-        <v>114.7404102</v>
+        <v>116.2114411</v>
       </c>
       <c r="N80">
-        <v>260.6929231333334</v>
+        <v>259.2218922333333</v>
       </c>
       <c r="O80">
-        <v>65.17323078333334</v>
+        <v>64.80547305833333</v>
       </c>
       <c r="P80">
-        <v>195.51969235</v>
+        <v>194.416419175</v>
       </c>
       <c r="Q80">
-        <v>277.41969235</v>
+        <v>276.316419175</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4627254014241336</v>
+        <v>0.4812225354713446</v>
       </c>
       <c r="T80">
-        <v>4.031987280515775</v>
+        <v>4.210868703786218</v>
       </c>
       <c r="U80">
         <v>0.0641</v>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.272023628632045</v>
+        <v>3.230605608016449</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1390359824489824</v>
+        <v>0.1387738765846553</v>
       </c>
       <c r="C81">
-        <v>970.987194977469</v>
+        <v>955.4952517384086</v>
       </c>
       <c r="D81">
-        <v>2645.158194977469</v>
+        <v>2652.615251738408</v>
       </c>
       <c r="E81">
-        <v>194.2710000000002</v>
+        <v>217.22</v>
       </c>
       <c r="F81">
-        <v>1812.971</v>
+        <v>1835.92</v>
       </c>
       <c r="G81">
         <v>138.8</v>
@@ -7917,28 +7917,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M81">
-        <v>116.2114411</v>
+        <v>117.682472</v>
       </c>
       <c r="N81">
-        <v>259.2218922333333</v>
+        <v>257.7508613333333</v>
       </c>
       <c r="O81">
-        <v>64.80547305833333</v>
+        <v>64.43771533333333</v>
       </c>
       <c r="P81">
-        <v>194.416419175</v>
+        <v>193.313146</v>
       </c>
       <c r="Q81">
-        <v>276.316419175</v>
+        <v>275.2131459999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4812225354713446</v>
+        <v>0.5015693829232766</v>
       </c>
       <c r="T81">
-        <v>4.210868703786218</v>
+        <v>4.407638269383705</v>
       </c>
       <c r="U81">
         <v>0.0641</v>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.230605608016449</v>
+        <v>3.190223037916244</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1387738765846553</v>
+        <v>0.1385117707203282</v>
       </c>
       <c r="C82">
-        <v>955.4952517384086</v>
+        <v>940.0454722568184</v>
       </c>
       <c r="D82">
-        <v>2652.615251738408</v>
+        <v>2660.114472256818</v>
       </c>
       <c r="E82">
-        <v>217.22</v>
+        <v>240.1690000000001</v>
       </c>
       <c r="F82">
-        <v>1835.92</v>
+        <v>1858.869</v>
       </c>
       <c r="G82">
         <v>138.8</v>
@@ -7999,28 +7999,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M82">
-        <v>117.682472</v>
+        <v>119.1535029</v>
       </c>
       <c r="N82">
-        <v>257.7508613333333</v>
+        <v>256.2798304333333</v>
       </c>
       <c r="O82">
-        <v>64.43771533333333</v>
+        <v>64.06995760833333</v>
       </c>
       <c r="P82">
-        <v>193.313146</v>
+        <v>192.209872825</v>
       </c>
       <c r="Q82">
-        <v>275.2131459999999</v>
+        <v>274.109872825</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5015693829232766</v>
+        <v>0.5240580037912014</v>
       </c>
       <c r="T82">
-        <v>4.407638269383705</v>
+        <v>4.625120420833559</v>
       </c>
       <c r="U82">
         <v>0.0641</v>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.190223037916244</v>
+        <v>3.150837568312339</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1385117707203282</v>
+        <v>0.1382496648560012</v>
       </c>
       <c r="C83">
-        <v>940.0454722568184</v>
+        <v>924.6382151505954</v>
       </c>
       <c r="D83">
-        <v>2660.114472256818</v>
+        <v>2667.656215150595</v>
       </c>
       <c r="E83">
-        <v>240.1690000000001</v>
+        <v>263.1180000000002</v>
       </c>
       <c r="F83">
-        <v>1858.869</v>
+        <v>1881.818</v>
       </c>
       <c r="G83">
         <v>138.8</v>
@@ -8081,28 +8081,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M83">
-        <v>119.1535029</v>
+        <v>120.6245338</v>
       </c>
       <c r="N83">
-        <v>256.2798304333333</v>
+        <v>254.8087995333333</v>
       </c>
       <c r="O83">
-        <v>64.06995760833333</v>
+        <v>63.70219988333333</v>
       </c>
       <c r="P83">
-        <v>192.209872825</v>
+        <v>191.10659965</v>
       </c>
       <c r="Q83">
-        <v>274.109872825</v>
+        <v>273.00659965</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5240580037912014</v>
+        <v>0.5490453603111178</v>
       </c>
       <c r="T83">
-        <v>4.625120420833559</v>
+        <v>4.866767255777841</v>
       </c>
       <c r="U83">
         <v>0.0641</v>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.150837568312339</v>
+        <v>3.112412719918286</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1382496648560012</v>
+        <v>0.1379875589916741</v>
       </c>
       <c r="C84">
-        <v>924.6382151505954</v>
+        <v>909.273843116096</v>
       </c>
       <c r="D84">
-        <v>2667.656215150595</v>
+        <v>2675.240843116096</v>
       </c>
       <c r="E84">
-        <v>263.1180000000002</v>
+        <v>286.0670000000002</v>
       </c>
       <c r="F84">
-        <v>1881.818</v>
+        <v>1904.767</v>
       </c>
       <c r="G84">
         <v>138.8</v>
@@ -8163,28 +8163,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M84">
-        <v>120.6245338</v>
+        <v>122.0955647</v>
       </c>
       <c r="N84">
-        <v>254.8087995333333</v>
+        <v>253.3377686333333</v>
       </c>
       <c r="O84">
-        <v>63.70219988333333</v>
+        <v>63.33444215833333</v>
       </c>
       <c r="P84">
-        <v>191.10659965</v>
+        <v>190.003326475</v>
       </c>
       <c r="Q84">
-        <v>273.00659965</v>
+        <v>271.903326475</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.5490453603111178</v>
+        <v>0.5769724058333775</v>
       </c>
       <c r="T84">
-        <v>4.866767255777841</v>
+        <v>5.136843130127334</v>
       </c>
       <c r="U84">
         <v>0.0641</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.112412719918286</v>
+        <v>3.074913771485536</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1379875589916741</v>
+        <v>0.1377254531273471</v>
       </c>
       <c r="C85">
-        <v>909.273843116096</v>
+        <v>893.9527229862829</v>
       </c>
       <c r="D85">
-        <v>2675.240843116096</v>
+        <v>2682.868722986283</v>
       </c>
       <c r="E85">
-        <v>286.0670000000002</v>
+        <v>309.0160000000003</v>
       </c>
       <c r="F85">
-        <v>1904.767</v>
+        <v>1927.716</v>
       </c>
       <c r="G85">
         <v>138.8</v>
@@ -8245,28 +8245,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M85">
-        <v>122.0955647</v>
+        <v>123.5665956</v>
       </c>
       <c r="N85">
-        <v>253.3377686333333</v>
+        <v>251.8667377333333</v>
       </c>
       <c r="O85">
-        <v>63.33444215833333</v>
+        <v>62.96668443333333</v>
       </c>
       <c r="P85">
-        <v>190.003326475</v>
+        <v>188.9000533</v>
       </c>
       <c r="Q85">
-        <v>271.903326475</v>
+        <v>270.8000532999999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.5769724058333775</v>
+        <v>0.6083903320459196</v>
       </c>
       <c r="T85">
-        <v>5.136843130127334</v>
+        <v>5.440678488770513</v>
       </c>
       <c r="U85">
         <v>0.0641</v>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.074913771485536</v>
+        <v>3.038307655158327</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1377254531273471</v>
+        <v>0.1374633472630201</v>
       </c>
       <c r="C86">
-        <v>893.9527229862842</v>
+        <v>878.6752257898688</v>
       </c>
       <c r="D86">
-        <v>2682.868722986284</v>
+        <v>2690.540225789869</v>
       </c>
       <c r="E86">
-        <v>309.0159999999998</v>
+        <v>331.9649999999999</v>
       </c>
       <c r="F86">
-        <v>1927.716</v>
+        <v>1950.665</v>
       </c>
       <c r="G86">
         <v>138.8</v>
@@ -8327,28 +8327,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M86">
-        <v>123.5665956</v>
+        <v>125.0376265</v>
       </c>
       <c r="N86">
-        <v>251.8667377333333</v>
+        <v>250.3957068333333</v>
       </c>
       <c r="O86">
-        <v>62.96668443333333</v>
+        <v>62.59892670833334</v>
       </c>
       <c r="P86">
-        <v>188.9000533</v>
+        <v>187.796780125</v>
       </c>
       <c r="Q86">
-        <v>270.8000532999999</v>
+        <v>269.696780125</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.6083903320459192</v>
+        <v>0.6439973150868004</v>
       </c>
       <c r="T86">
-        <v>5.440678488770509</v>
+        <v>5.785025228566112</v>
       </c>
       <c r="U86">
         <v>0.0641</v>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.038307655158328</v>
+        <v>3.002562859215289</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1374633472630201</v>
+        <v>0.142232241398693</v>
       </c>
       <c r="C87">
-        <v>878.6752257898688</v>
+        <v>722.6700889786034</v>
       </c>
       <c r="D87">
-        <v>2690.540225789869</v>
+        <v>2557.484088978603</v>
       </c>
       <c r="E87">
-        <v>331.9649999999999</v>
+        <v>354.914</v>
       </c>
       <c r="F87">
-        <v>1950.665</v>
+        <v>1973.614</v>
       </c>
       <c r="G87">
         <v>138.8</v>
@@ -8409,45 +8409,45 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M87">
-        <v>125.0376265</v>
+        <v>141.9028466</v>
       </c>
       <c r="N87">
-        <v>250.3957068333333</v>
+        <v>233.5304867333333</v>
       </c>
       <c r="O87">
-        <v>62.59892670833334</v>
+        <v>58.38262168333333</v>
       </c>
       <c r="P87">
-        <v>187.796780125</v>
+        <v>175.14786505</v>
       </c>
       <c r="Q87">
-        <v>269.696780125</v>
+        <v>257.04786505</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.6439973150868004</v>
+        <v>0.6846910099906642</v>
       </c>
       <c r="T87">
-        <v>5.785025228566112</v>
+        <v>6.178564359761085</v>
       </c>
       <c r="U87">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V87">
         <v>0.25</v>
       </c>
       <c r="W87">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y87">
-        <v>3.002562859215289</v>
+        <v>2.645706850346816</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.142232241398693</v>
+        <v>0.1420286355343659</v>
       </c>
       <c r="C88">
-        <v>722.6700889786034</v>
+        <v>705.1323551318401</v>
       </c>
       <c r="D88">
-        <v>2557.484088978603</v>
+        <v>2562.89535513184</v>
       </c>
       <c r="E88">
-        <v>354.914</v>
+        <v>377.8630000000001</v>
       </c>
       <c r="F88">
-        <v>1973.614</v>
+        <v>1996.563</v>
       </c>
       <c r="G88">
         <v>138.8</v>
@@ -8491,28 +8491,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M88">
-        <v>141.9028466</v>
+        <v>143.5528797</v>
       </c>
       <c r="N88">
-        <v>233.5304867333333</v>
+        <v>231.8804536333333</v>
       </c>
       <c r="O88">
-        <v>58.38262168333333</v>
+        <v>57.97011340833333</v>
       </c>
       <c r="P88">
-        <v>175.14786505</v>
+        <v>173.910340225</v>
       </c>
       <c r="Q88">
-        <v>257.04786505</v>
+        <v>255.810340225</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.6846910099906642</v>
+        <v>0.7316452733412764</v>
       </c>
       <c r="T88">
-        <v>6.178564359761085</v>
+        <v>6.632647972678361</v>
       </c>
       <c r="U88">
         <v>0.07190000000000001</v>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.645706850346816</v>
+        <v>2.615296426779611</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1420286355343659</v>
+        <v>0.1418250296700389</v>
       </c>
       <c r="C89">
-        <v>705.1323551318401</v>
+        <v>687.6175687504597</v>
       </c>
       <c r="D89">
-        <v>2562.89535513184</v>
+        <v>2568.32956875046</v>
       </c>
       <c r="E89">
-        <v>377.8630000000001</v>
+        <v>400.8120000000001</v>
       </c>
       <c r="F89">
-        <v>1996.563</v>
+        <v>2019.512</v>
       </c>
       <c r="G89">
         <v>138.8</v>
@@ -8573,28 +8573,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M89">
-        <v>143.5528797</v>
+        <v>145.2029128</v>
       </c>
       <c r="N89">
-        <v>231.8804536333333</v>
+        <v>230.2304205333333</v>
       </c>
       <c r="O89">
-        <v>57.97011340833333</v>
+        <v>57.55760513333333</v>
       </c>
       <c r="P89">
-        <v>173.910340225</v>
+        <v>172.6728154</v>
       </c>
       <c r="Q89">
-        <v>255.810340225</v>
+        <v>254.5728154</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.7316452733412764</v>
+        <v>0.7864252472503243</v>
       </c>
       <c r="T89">
-        <v>6.632647972678361</v>
+        <v>7.16241218774852</v>
       </c>
       <c r="U89">
         <v>0.07190000000000001</v>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.615296426779611</v>
+        <v>2.585577149202569</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1418250296700389</v>
+        <v>0.1416214238057119</v>
       </c>
       <c r="C90">
-        <v>687.6175687504597</v>
+        <v>670.1258761140245</v>
       </c>
       <c r="D90">
-        <v>2568.32956875046</v>
+        <v>2573.786876114024</v>
       </c>
       <c r="E90">
-        <v>400.8120000000001</v>
+        <v>423.761</v>
       </c>
       <c r="F90">
-        <v>2019.512</v>
+        <v>2042.461</v>
       </c>
       <c r="G90">
         <v>138.8</v>
@@ -8655,28 +8655,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M90">
-        <v>145.2029128</v>
+        <v>146.8529459</v>
       </c>
       <c r="N90">
-        <v>230.2304205333333</v>
+        <v>228.5803874333333</v>
       </c>
       <c r="O90">
-        <v>57.55760513333333</v>
+        <v>57.14509685833333</v>
       </c>
       <c r="P90">
-        <v>172.6728154</v>
+        <v>171.435290575</v>
       </c>
       <c r="Q90">
-        <v>254.5728154</v>
+        <v>253.335290575</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.7864252472503243</v>
+        <v>0.8511652164155623</v>
       </c>
       <c r="T90">
-        <v>7.16241218774852</v>
+        <v>7.788497169195068</v>
       </c>
       <c r="U90">
         <v>0.07190000000000001</v>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.585577149202569</v>
+        <v>2.556525720559844</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1416214238057119</v>
+        <v>0.1414178179413848</v>
       </c>
       <c r="C91">
-        <v>670.1258761140245</v>
+        <v>652.6574247480253</v>
       </c>
       <c r="D91">
-        <v>2573.786876114024</v>
+        <v>2579.267424748025</v>
       </c>
       <c r="E91">
-        <v>423.761</v>
+        <v>446.7100000000003</v>
       </c>
       <c r="F91">
-        <v>2042.461</v>
+        <v>2065.41</v>
       </c>
       <c r="G91">
         <v>138.8</v>
@@ -8737,28 +8737,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M91">
-        <v>146.8529459</v>
+        <v>148.502979</v>
       </c>
       <c r="N91">
-        <v>228.5803874333333</v>
+        <v>226.9303543333333</v>
       </c>
       <c r="O91">
-        <v>57.14509685833333</v>
+        <v>56.73258858333332</v>
       </c>
       <c r="P91">
-        <v>171.435290575</v>
+        <v>170.19776575</v>
       </c>
       <c r="Q91">
-        <v>253.335290575</v>
+        <v>252.09776575</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.8511652164155623</v>
+        <v>0.9288531794138483</v>
       </c>
       <c r="T91">
-        <v>7.788497169195068</v>
+        <v>8.539799146930928</v>
       </c>
       <c r="U91">
         <v>0.07190000000000001</v>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.556525720559844</v>
+        <v>2.52811987922029</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1414178179413848</v>
+        <v>0.1412142120770578</v>
       </c>
       <c r="C92">
-        <v>652.6574247480253</v>
+        <v>635.2123634371824</v>
       </c>
       <c r="D92">
-        <v>2579.267424748025</v>
+        <v>2584.771363437183</v>
       </c>
       <c r="E92">
-        <v>446.7100000000003</v>
+        <v>469.6590000000003</v>
       </c>
       <c r="F92">
-        <v>2065.41</v>
+        <v>2088.359</v>
       </c>
       <c r="G92">
         <v>138.8</v>
@@ -8819,28 +8819,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M92">
-        <v>148.502979</v>
+        <v>150.1530121</v>
       </c>
       <c r="N92">
-        <v>226.9303543333333</v>
+        <v>225.2803212333333</v>
       </c>
       <c r="O92">
-        <v>56.73258858333332</v>
+        <v>56.32008030833332</v>
       </c>
       <c r="P92">
-        <v>170.19776575</v>
+        <v>168.960240925</v>
       </c>
       <c r="Q92">
-        <v>252.09776575</v>
+        <v>250.8602409249999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.9288531794138483</v>
+        <v>1.023805134189531</v>
       </c>
       <c r="T92">
-        <v>8.539799146930928</v>
+        <v>9.458057119719202</v>
       </c>
       <c r="U92">
         <v>0.07190000000000001</v>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.52811987922029</v>
+        <v>2.500338342086001</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1412142120770578</v>
+        <v>0.1437016062127307</v>
       </c>
       <c r="C93">
-        <v>635.2123634371824</v>
+        <v>546.5918654895531</v>
       </c>
       <c r="D93">
-        <v>2584.771363437183</v>
+        <v>2519.099865489553</v>
       </c>
       <c r="E93">
-        <v>469.6590000000003</v>
+        <v>492.6079999999999</v>
       </c>
       <c r="F93">
-        <v>2088.359</v>
+        <v>2111.308</v>
       </c>
       <c r="G93">
         <v>138.8</v>
@@ -8901,45 +8901,45 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M93">
-        <v>150.1530121</v>
+        <v>160.0371464</v>
       </c>
       <c r="N93">
-        <v>225.2803212333333</v>
+        <v>215.3961869333333</v>
       </c>
       <c r="O93">
-        <v>56.32008030833332</v>
+        <v>53.84904673333333</v>
       </c>
       <c r="P93">
-        <v>168.960240925</v>
+        <v>161.5471402</v>
       </c>
       <c r="Q93">
-        <v>250.8602409249999</v>
+        <v>243.4471402</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.023805134189531</v>
+        <v>1.142495077659135</v>
       </c>
       <c r="T93">
-        <v>9.458057119719202</v>
+        <v>10.60587958570454</v>
       </c>
       <c r="U93">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V93">
         <v>0.25</v>
       </c>
       <c r="W93">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y93">
-        <v>2.500338342086001</v>
+        <v>2.345913694280501</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1437016062127307</v>
+        <v>0.1435272503484037</v>
       </c>
       <c r="C94">
-        <v>546.5918654895531</v>
+        <v>528.1372090099908</v>
       </c>
       <c r="D94">
-        <v>2519.099865489553</v>
+        <v>2523.594209009991</v>
       </c>
       <c r="E94">
-        <v>492.6079999999999</v>
+        <v>515.557</v>
       </c>
       <c r="F94">
-        <v>2111.308</v>
+        <v>2134.257</v>
       </c>
       <c r="G94">
         <v>138.8</v>
@@ -8983,28 +8983,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M94">
-        <v>160.0371464</v>
+        <v>161.7766806</v>
       </c>
       <c r="N94">
-        <v>215.3961869333333</v>
+        <v>213.6566527333333</v>
       </c>
       <c r="O94">
-        <v>53.84904673333333</v>
+        <v>53.41416318333333</v>
       </c>
       <c r="P94">
-        <v>161.5471402</v>
+        <v>160.24248955</v>
       </c>
       <c r="Q94">
-        <v>243.4471402</v>
+        <v>242.14248955</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.142495077659135</v>
+        <v>1.295096433548625</v>
       </c>
       <c r="T94">
-        <v>10.60587958570454</v>
+        <v>12.0816513276857</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.345913694280501</v>
+        <v>2.320688815847377</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1435272503484037</v>
+        <v>0.1433528944840766</v>
       </c>
       <c r="C95">
-        <v>528.1372090099908</v>
+        <v>509.698617971711</v>
       </c>
       <c r="D95">
-        <v>2523.594209009991</v>
+        <v>2528.104617971711</v>
       </c>
       <c r="E95">
-        <v>515.557</v>
+        <v>538.5060000000001</v>
       </c>
       <c r="F95">
-        <v>2134.257</v>
+        <v>2157.206</v>
       </c>
       <c r="G95">
         <v>138.8</v>
@@ -9065,28 +9065,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M95">
-        <v>161.7766806</v>
+        <v>163.5162148</v>
       </c>
       <c r="N95">
-        <v>213.6566527333333</v>
+        <v>211.9171185333333</v>
       </c>
       <c r="O95">
-        <v>53.41416318333333</v>
+        <v>52.97927963333333</v>
       </c>
       <c r="P95">
-        <v>160.24248955</v>
+        <v>158.9378389</v>
       </c>
       <c r="Q95">
-        <v>242.14248955</v>
+        <v>240.8378389</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.295096433548625</v>
+        <v>1.498564908067945</v>
       </c>
       <c r="T95">
-        <v>12.0816513276857</v>
+        <v>14.04934698366057</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.320688815847377</v>
+        <v>2.296000636955383</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1433528944840766</v>
+        <v>0.1431785386197496</v>
       </c>
       <c r="C96">
-        <v>509.698617971711</v>
+        <v>491.2761786700271</v>
       </c>
       <c r="D96">
-        <v>2528.104617971711</v>
+        <v>2532.631178670027</v>
       </c>
       <c r="E96">
-        <v>538.5060000000001</v>
+        <v>561.4550000000002</v>
       </c>
       <c r="F96">
-        <v>2157.206</v>
+        <v>2180.155</v>
       </c>
       <c r="G96">
         <v>138.8</v>
@@ -9147,28 +9147,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M96">
-        <v>163.5162148</v>
+        <v>165.255749</v>
       </c>
       <c r="N96">
-        <v>211.9171185333333</v>
+        <v>210.1775843333333</v>
       </c>
       <c r="O96">
-        <v>52.97927963333333</v>
+        <v>52.54439608333333</v>
       </c>
       <c r="P96">
-        <v>158.9378389</v>
+        <v>157.63318825</v>
       </c>
       <c r="Q96">
-        <v>240.8378389</v>
+        <v>239.53318825</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.498564908067945</v>
+        <v>1.783420772394994</v>
       </c>
       <c r="T96">
-        <v>14.04934698366057</v>
+        <v>16.8041209020254</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.296000636955383</v>
+        <v>2.271832209197958</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1431785386197496</v>
+        <v>0.1430041827554225</v>
       </c>
       <c r="C97">
-        <v>491.2761786700271</v>
+        <v>472.8699780194102</v>
       </c>
       <c r="D97">
-        <v>2532.631178670027</v>
+        <v>2537.17397801941</v>
       </c>
       <c r="E97">
-        <v>561.4550000000002</v>
+        <v>584.4040000000002</v>
       </c>
       <c r="F97">
-        <v>2180.155</v>
+        <v>2203.104</v>
       </c>
       <c r="G97">
         <v>138.8</v>
@@ -9229,28 +9229,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M97">
-        <v>165.255749</v>
+        <v>166.9952832</v>
       </c>
       <c r="N97">
-        <v>210.1775843333333</v>
+        <v>208.4380501333333</v>
       </c>
       <c r="O97">
-        <v>52.54439608333333</v>
+        <v>52.10951253333332</v>
       </c>
       <c r="P97">
-        <v>157.63318825</v>
+        <v>156.3285376</v>
       </c>
       <c r="Q97">
-        <v>239.53318825</v>
+        <v>238.2285376</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.783420772394994</v>
+        <v>2.210704568885567</v>
       </c>
       <c r="T97">
-        <v>16.8041209020254</v>
+        <v>20.93628177957264</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.271832209197958</v>
+        <v>2.248167290352146</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1430041827554225</v>
+        <v>0.1428298268910955</v>
       </c>
       <c r="C98">
-        <v>472.8699780194106</v>
+        <v>454.4801035590463</v>
       </c>
       <c r="D98">
-        <v>2537.17397801941</v>
+        <v>2541.733103559046</v>
       </c>
       <c r="E98">
-        <v>584.4039999999998</v>
+        <v>607.3529999999998</v>
       </c>
       <c r="F98">
-        <v>2203.104</v>
+        <v>2226.053</v>
       </c>
       <c r="G98">
         <v>138.8</v>
@@ -9311,28 +9311,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M98">
-        <v>166.9952832</v>
+        <v>168.7348174</v>
       </c>
       <c r="N98">
-        <v>208.4380501333333</v>
+        <v>206.6985159333333</v>
       </c>
       <c r="O98">
-        <v>52.10951253333334</v>
+        <v>51.67462898333333</v>
       </c>
       <c r="P98">
-        <v>156.3285376</v>
+        <v>155.02388695</v>
       </c>
       <c r="Q98">
-        <v>238.2285376</v>
+        <v>236.92388695</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.210704568885561</v>
+        <v>2.92284422970318</v>
       </c>
       <c r="T98">
-        <v>20.93628177957258</v>
+        <v>27.82321657548461</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.248167290352146</v>
+        <v>2.224990307977382</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1428298268910955</v>
+        <v>0.1426554710267684</v>
       </c>
       <c r="C99">
-        <v>454.4801035590463</v>
+        <v>436.1066434584627</v>
       </c>
       <c r="D99">
-        <v>2541.733103559046</v>
+        <v>2546.308643458462</v>
       </c>
       <c r="E99">
-        <v>607.3529999999998</v>
+        <v>630.3019999999999</v>
       </c>
       <c r="F99">
-        <v>2226.053</v>
+        <v>2249.002</v>
       </c>
       <c r="G99">
         <v>138.8</v>
@@ -9393,28 +9393,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M99">
-        <v>168.7348174</v>
+        <v>170.4743516</v>
       </c>
       <c r="N99">
-        <v>206.6985159333333</v>
+        <v>204.9589817333333</v>
       </c>
       <c r="O99">
-        <v>51.67462898333333</v>
+        <v>51.23974543333333</v>
       </c>
       <c r="P99">
-        <v>155.02388695</v>
+        <v>153.7192363</v>
       </c>
       <c r="Q99">
-        <v>236.92388695</v>
+        <v>235.6192363</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.92284422970318</v>
+        <v>4.347123551338417</v>
       </c>
       <c r="T99">
-        <v>27.82321657548461</v>
+        <v>41.59708616730867</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.224990307977382</v>
+        <v>2.202286325242919</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1426554710267684</v>
+        <v>0.1424811151624414</v>
       </c>
       <c r="C100">
-        <v>436.1066434584627</v>
+        <v>417.7496865232083</v>
       </c>
       <c r="D100">
-        <v>2546.308643458462</v>
+        <v>2550.900686523208</v>
       </c>
       <c r="E100">
-        <v>630.3019999999999</v>
+        <v>653.251</v>
       </c>
       <c r="F100">
-        <v>2249.002</v>
+        <v>2271.951</v>
       </c>
       <c r="G100">
         <v>138.8</v>
@@ -9475,28 +9475,28 @@
         <v>375.4333333333333</v>
       </c>
       <c r="M100">
-        <v>170.4743516</v>
+        <v>172.2138858</v>
       </c>
       <c r="N100">
-        <v>204.9589817333333</v>
+        <v>203.2194475333333</v>
       </c>
       <c r="O100">
-        <v>51.23974543333333</v>
+        <v>50.80486188333333</v>
       </c>
       <c r="P100">
-        <v>153.7192363</v>
+        <v>152.41458565</v>
       </c>
       <c r="Q100">
-        <v>235.6192363</v>
+        <v>234.31458565</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.347123551338417</v>
+        <v>8.619961516244132</v>
       </c>
       <c r="T100">
-        <v>41.59708616730867</v>
+        <v>82.91869494278087</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.202286325242919</v>
+        <v>2.180041008826324</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1424811151624414</v>
-      </c>
-      <c r="C101">
-        <v>417.7496865232083</v>
-      </c>
-      <c r="D101">
-        <v>2550.900686523208</v>
-      </c>
-      <c r="E101">
-        <v>653.251</v>
-      </c>
-      <c r="F101">
-        <v>2271.951</v>
-      </c>
-      <c r="G101">
-        <v>138.8</v>
-      </c>
-      <c r="H101">
-        <v>676.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>457.3333333333333</v>
-      </c>
-      <c r="K101">
-        <v>81.89999999999998</v>
-      </c>
-      <c r="L101">
-        <v>375.4333333333333</v>
-      </c>
-      <c r="M101">
-        <v>172.2138858</v>
-      </c>
-      <c r="N101">
-        <v>203.2194475333333</v>
-      </c>
-      <c r="O101">
-        <v>50.80486188333333</v>
-      </c>
-      <c r="P101">
-        <v>152.41458565</v>
-      </c>
-      <c r="Q101">
-        <v>234.31458565</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>8.619961516244132</v>
-      </c>
-      <c r="T101">
-        <v>82.91869494278087</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.25</v>
-      </c>
-      <c r="W101">
-        <v>0.05685</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.180041008826324</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
